--- a/data/CONTROL_DE_VIVENCIA.xlsx
+++ b/data/CONTROL_DE_VIVENCIA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jronquilla\Desktop\control-vivencia\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jronquilla\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDED8A5A-CB75-464F-BFFE-CAE48043E05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D87343-E7B8-480C-AA0C-BA5275DBFD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8329" uniqueCount="1463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8322" uniqueCount="1465">
   <si>
     <t>ABIGAIL  MEJIA CHOQUECALLATA VDA.DE MUÑOZ</t>
   </si>
@@ -4426,6 +4426,12 @@
   </si>
   <si>
     <t>COMUNICARSE AL NUMERO 69967103</t>
+  </si>
+  <si>
+    <t>APROXIMARSE EN LA OFICINA</t>
+  </si>
+  <si>
+    <t>COMUNICARSE AL NUMERO 69776216</t>
   </si>
 </sst>
 </file>
@@ -11447,7 +11453,7 @@
         <v>1421</v>
       </c>
       <c r="G272" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -11470,7 +11476,7 @@
         <v>1421</v>
       </c>
       <c r="G273" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -11493,7 +11499,7 @@
         <v>1421</v>
       </c>
       <c r="G274" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -11516,7 +11522,7 @@
         <v>1421</v>
       </c>
       <c r="G275" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -11539,7 +11545,7 @@
         <v>1421</v>
       </c>
       <c r="G276" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -11562,7 +11568,7 @@
         <v>1421</v>
       </c>
       <c r="G277" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11585,7 +11591,7 @@
         <v>1421</v>
       </c>
       <c r="G278" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11608,7 +11614,7 @@
         <v>1421</v>
       </c>
       <c r="G279" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11631,7 +11637,7 @@
         <v>1421</v>
       </c>
       <c r="G280" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11654,7 +11660,7 @@
         <v>1421</v>
       </c>
       <c r="G281" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11677,7 +11683,7 @@
         <v>1421</v>
       </c>
       <c r="G282" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11700,7 +11706,7 @@
         <v>1421</v>
       </c>
       <c r="G283" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11723,7 +11729,7 @@
         <v>1421</v>
       </c>
       <c r="G284" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11746,7 +11752,7 @@
         <v>1421</v>
       </c>
       <c r="G285" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11769,7 +11775,7 @@
         <v>1421</v>
       </c>
       <c r="G286" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11792,7 +11798,7 @@
         <v>1421</v>
       </c>
       <c r="G287" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11815,7 +11821,7 @@
         <v>1421</v>
       </c>
       <c r="G288" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11838,7 +11844,7 @@
         <v>1421</v>
       </c>
       <c r="G289" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11861,7 +11867,7 @@
         <v>1421</v>
       </c>
       <c r="G290" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11884,7 +11890,7 @@
         <v>1421</v>
       </c>
       <c r="G291" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11907,7 +11913,7 @@
         <v>1421</v>
       </c>
       <c r="G292" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11930,7 +11936,7 @@
         <v>1421</v>
       </c>
       <c r="G293" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11953,7 +11959,7 @@
         <v>1421</v>
       </c>
       <c r="G294" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11976,7 +11982,7 @@
         <v>1421</v>
       </c>
       <c r="G295" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11999,7 +12005,7 @@
         <v>1421</v>
       </c>
       <c r="G296" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -12022,7 +12028,7 @@
         <v>1421</v>
       </c>
       <c r="G297" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -12045,7 +12051,7 @@
         <v>1421</v>
       </c>
       <c r="G298" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -12068,7 +12074,7 @@
         <v>1421</v>
       </c>
       <c r="G299" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -12091,7 +12097,7 @@
         <v>1421</v>
       </c>
       <c r="G300" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -12114,7 +12120,7 @@
         <v>1421</v>
       </c>
       <c r="G301" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -12137,7 +12143,7 @@
         <v>1421</v>
       </c>
       <c r="G302" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -12160,7 +12166,7 @@
         <v>1421</v>
       </c>
       <c r="G303" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -12183,7 +12189,7 @@
         <v>1421</v>
       </c>
       <c r="G304" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -12206,7 +12212,7 @@
         <v>1421</v>
       </c>
       <c r="G305" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -12229,7 +12235,7 @@
         <v>1421</v>
       </c>
       <c r="G306" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -12252,7 +12258,7 @@
         <v>1421</v>
       </c>
       <c r="G307" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -12275,7 +12281,7 @@
         <v>1421</v>
       </c>
       <c r="G308" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -12298,7 +12304,7 @@
         <v>1421</v>
       </c>
       <c r="G309" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -12321,7 +12327,7 @@
         <v>1421</v>
       </c>
       <c r="G310" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -12344,7 +12350,7 @@
         <v>1421</v>
       </c>
       <c r="G311" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -12367,7 +12373,7 @@
         <v>1421</v>
       </c>
       <c r="G312" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -12390,7 +12396,7 @@
         <v>1421</v>
       </c>
       <c r="G313" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -12413,7 +12419,7 @@
         <v>1421</v>
       </c>
       <c r="G314" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -12436,7 +12442,7 @@
         <v>1421</v>
       </c>
       <c r="G315" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -12459,7 +12465,7 @@
         <v>1421</v>
       </c>
       <c r="G316" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -12482,7 +12488,7 @@
         <v>1421</v>
       </c>
       <c r="G317" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -12505,7 +12511,7 @@
         <v>1421</v>
       </c>
       <c r="G318" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -12528,7 +12534,7 @@
         <v>1421</v>
       </c>
       <c r="G319" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -12551,7 +12557,7 @@
         <v>1421</v>
       </c>
       <c r="G320" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -12574,7 +12580,7 @@
         <v>1421</v>
       </c>
       <c r="G321" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12597,7 +12603,7 @@
         <v>1421</v>
       </c>
       <c r="G322" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12620,7 +12626,7 @@
         <v>1421</v>
       </c>
       <c r="G323" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12643,7 +12649,7 @@
         <v>1421</v>
       </c>
       <c r="G324" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12666,7 +12672,7 @@
         <v>1421</v>
       </c>
       <c r="G325" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12689,7 +12695,7 @@
         <v>1421</v>
       </c>
       <c r="G326" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12712,7 +12718,7 @@
         <v>1421</v>
       </c>
       <c r="G327" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12735,7 +12741,7 @@
         <v>1421</v>
       </c>
       <c r="G328" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12758,7 +12764,7 @@
         <v>1421</v>
       </c>
       <c r="G329" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12781,7 +12787,7 @@
         <v>1421</v>
       </c>
       <c r="G330" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12804,7 +12810,7 @@
         <v>1421</v>
       </c>
       <c r="G331" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12827,7 +12833,7 @@
         <v>1421</v>
       </c>
       <c r="G332" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12850,7 +12856,7 @@
         <v>1421</v>
       </c>
       <c r="G333" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12873,7 +12879,7 @@
         <v>1421</v>
       </c>
       <c r="G334" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12896,7 +12902,7 @@
         <v>1421</v>
       </c>
       <c r="G335" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
@@ -12919,7 +12925,7 @@
         <v>1421</v>
       </c>
       <c r="G336" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
@@ -12942,7 +12948,7 @@
         <v>1421</v>
       </c>
       <c r="G337" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
@@ -12965,7 +12971,7 @@
         <v>1421</v>
       </c>
       <c r="G338" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
@@ -12988,7 +12994,7 @@
         <v>1421</v>
       </c>
       <c r="G339" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.3">
@@ -13011,7 +13017,7 @@
         <v>1421</v>
       </c>
       <c r="G340" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
@@ -13034,7 +13040,7 @@
         <v>1421</v>
       </c>
       <c r="G341" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
@@ -13057,7 +13063,7 @@
         <v>1421</v>
       </c>
       <c r="G342" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
@@ -13080,7 +13086,7 @@
         <v>1421</v>
       </c>
       <c r="G343" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.3">
@@ -13103,7 +13109,7 @@
         <v>1421</v>
       </c>
       <c r="G344" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.3">
@@ -13126,7 +13132,7 @@
         <v>1421</v>
       </c>
       <c r="G345" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.3">
@@ -13149,7 +13155,7 @@
         <v>1421</v>
       </c>
       <c r="G346" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.3">
@@ -13172,7 +13178,7 @@
         <v>1421</v>
       </c>
       <c r="G347" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
@@ -13195,7 +13201,7 @@
         <v>1421</v>
       </c>
       <c r="G348" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
@@ -13218,7 +13224,7 @@
         <v>1421</v>
       </c>
       <c r="G349" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
@@ -13241,7 +13247,7 @@
         <v>1421</v>
       </c>
       <c r="G350" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
@@ -13264,7 +13270,7 @@
         <v>1421</v>
       </c>
       <c r="G351" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
@@ -13287,7 +13293,7 @@
         <v>1421</v>
       </c>
       <c r="G352" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.3">
@@ -13310,7 +13316,7 @@
         <v>1421</v>
       </c>
       <c r="G353" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.3">
@@ -13333,7 +13339,7 @@
         <v>1421</v>
       </c>
       <c r="G354" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.3">
@@ -13356,7 +13362,7 @@
         <v>1421</v>
       </c>
       <c r="G355" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.3">
@@ -13379,7 +13385,7 @@
         <v>1421</v>
       </c>
       <c r="G356" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.3">
@@ -13402,7 +13408,7 @@
         <v>1421</v>
       </c>
       <c r="G357" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.3">
@@ -13425,7 +13431,7 @@
         <v>1421</v>
       </c>
       <c r="G358" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.3">
@@ -13448,7 +13454,7 @@
         <v>1421</v>
       </c>
       <c r="G359" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.3">
@@ -13471,7 +13477,7 @@
         <v>1421</v>
       </c>
       <c r="G360" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.3">
@@ -13494,7 +13500,7 @@
         <v>1421</v>
       </c>
       <c r="G361" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
@@ -13517,7 +13523,7 @@
         <v>1421</v>
       </c>
       <c r="G362" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
@@ -13540,7 +13546,7 @@
         <v>1421</v>
       </c>
       <c r="G363" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.3">
@@ -13563,7 +13569,7 @@
         <v>1421</v>
       </c>
       <c r="G364" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.3">
@@ -13586,7 +13592,7 @@
         <v>1421</v>
       </c>
       <c r="G365" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.3">
@@ -13609,7 +13615,7 @@
         <v>1421</v>
       </c>
       <c r="G366" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.3">
@@ -13632,7 +13638,7 @@
         <v>1421</v>
       </c>
       <c r="G367" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.3">
@@ -13655,7 +13661,7 @@
         <v>1421</v>
       </c>
       <c r="G368" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
@@ -13678,7 +13684,7 @@
         <v>1421</v>
       </c>
       <c r="G369" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
@@ -13701,7 +13707,7 @@
         <v>1421</v>
       </c>
       <c r="G370" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
@@ -13724,7 +13730,7 @@
         <v>1421</v>
       </c>
       <c r="G371" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.3">
@@ -13747,7 +13753,7 @@
         <v>1421</v>
       </c>
       <c r="G372" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.3">
@@ -13770,7 +13776,7 @@
         <v>1421</v>
       </c>
       <c r="G373" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.3">
@@ -13793,7 +13799,7 @@
         <v>1421</v>
       </c>
       <c r="G374" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.3">
@@ -13816,7 +13822,7 @@
         <v>1421</v>
       </c>
       <c r="G375" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.3">
@@ -13839,7 +13845,7 @@
         <v>1421</v>
       </c>
       <c r="G376" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.3">
@@ -13862,7 +13868,7 @@
         <v>1421</v>
       </c>
       <c r="G377" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.3">
@@ -13885,7 +13891,7 @@
         <v>1421</v>
       </c>
       <c r="G378" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.3">
@@ -13908,7 +13914,7 @@
         <v>1421</v>
       </c>
       <c r="G379" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.3">
@@ -13931,7 +13937,7 @@
         <v>1421</v>
       </c>
       <c r="G380" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.3">
@@ -13954,7 +13960,7 @@
         <v>1421</v>
       </c>
       <c r="G381" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.3">
@@ -13977,7 +13983,7 @@
         <v>1421</v>
       </c>
       <c r="G382" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.3">
@@ -14000,7 +14006,7 @@
         <v>1421</v>
       </c>
       <c r="G383" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.3">
@@ -14023,7 +14029,7 @@
         <v>1421</v>
       </c>
       <c r="G384" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.3">
@@ -14046,7 +14052,7 @@
         <v>1421</v>
       </c>
       <c r="G385" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.3">
@@ -14069,7 +14075,7 @@
         <v>1421</v>
       </c>
       <c r="G386" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.3">
@@ -14092,7 +14098,7 @@
         <v>1421</v>
       </c>
       <c r="G387" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.3">
@@ -14115,7 +14121,7 @@
         <v>1421</v>
       </c>
       <c r="G388" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.3">
@@ -14138,7 +14144,7 @@
         <v>1421</v>
       </c>
       <c r="G389" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.3">
@@ -14161,7 +14167,7 @@
         <v>1421</v>
       </c>
       <c r="G390" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.3">
@@ -14184,7 +14190,7 @@
         <v>1421</v>
       </c>
       <c r="G391" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.3">
@@ -14207,7 +14213,7 @@
         <v>1421</v>
       </c>
       <c r="G392" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.3">
@@ -14230,7 +14236,7 @@
         <v>1421</v>
       </c>
       <c r="G393" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.3">
@@ -14253,7 +14259,7 @@
         <v>1421</v>
       </c>
       <c r="G394" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.3">
@@ -14276,7 +14282,7 @@
         <v>1421</v>
       </c>
       <c r="G395" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.3">
@@ -14299,7 +14305,7 @@
         <v>1421</v>
       </c>
       <c r="G396" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
@@ -14322,7 +14328,7 @@
         <v>1421</v>
       </c>
       <c r="G397" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
@@ -14345,7 +14351,7 @@
         <v>1421</v>
       </c>
       <c r="G398" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.3">
@@ -14368,7 +14374,7 @@
         <v>1421</v>
       </c>
       <c r="G399" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.3">
@@ -14391,7 +14397,7 @@
         <v>1421</v>
       </c>
       <c r="G400" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.3">
@@ -14414,7 +14420,7 @@
         <v>1421</v>
       </c>
       <c r="G401" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.3">
@@ -14437,7 +14443,7 @@
         <v>1421</v>
       </c>
       <c r="G402" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.3">
@@ -14460,7 +14466,7 @@
         <v>1421</v>
       </c>
       <c r="G403" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.3">
@@ -14483,7 +14489,7 @@
         <v>1421</v>
       </c>
       <c r="G404" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.3">
@@ -14506,7 +14512,7 @@
         <v>1421</v>
       </c>
       <c r="G405" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.3">
@@ -14529,7 +14535,7 @@
         <v>1421</v>
       </c>
       <c r="G406" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.3">
@@ -14552,7 +14558,7 @@
         <v>1421</v>
       </c>
       <c r="G407" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.3">
@@ -14575,7 +14581,7 @@
         <v>1421</v>
       </c>
       <c r="G408" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.3">
@@ -14598,7 +14604,7 @@
         <v>1421</v>
       </c>
       <c r="G409" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.3">
@@ -14621,7 +14627,7 @@
         <v>1421</v>
       </c>
       <c r="G410" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.3">
@@ -14644,7 +14650,7 @@
         <v>1421</v>
       </c>
       <c r="G411" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.3">
@@ -14667,7 +14673,7 @@
         <v>1421</v>
       </c>
       <c r="G412" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.3">
@@ -14690,7 +14696,7 @@
         <v>1421</v>
       </c>
       <c r="G413" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.3">
@@ -14713,7 +14719,7 @@
         <v>1421</v>
       </c>
       <c r="G414" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.3">
@@ -14736,7 +14742,7 @@
         <v>1421</v>
       </c>
       <c r="G415" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.3">
@@ -14759,7 +14765,7 @@
         <v>1421</v>
       </c>
       <c r="G416" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.3">
@@ -14782,7 +14788,7 @@
         <v>1421</v>
       </c>
       <c r="G417" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.3">
@@ -14805,7 +14811,7 @@
         <v>1421</v>
       </c>
       <c r="G418" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
@@ -14828,7 +14834,7 @@
         <v>1421</v>
       </c>
       <c r="G419" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
@@ -14851,7 +14857,7 @@
         <v>1421</v>
       </c>
       <c r="G420" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
@@ -14874,7 +14880,7 @@
         <v>1421</v>
       </c>
       <c r="G421" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
@@ -14897,7 +14903,7 @@
         <v>1421</v>
       </c>
       <c r="G422" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
@@ -14920,7 +14926,7 @@
         <v>1421</v>
       </c>
       <c r="G423" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
@@ -14943,7 +14949,7 @@
         <v>1421</v>
       </c>
       <c r="G424" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
@@ -14966,7 +14972,7 @@
         <v>1421</v>
       </c>
       <c r="G425" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
@@ -14989,7 +14995,7 @@
         <v>1421</v>
       </c>
       <c r="G426" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
@@ -15012,7 +15018,7 @@
         <v>1421</v>
       </c>
       <c r="G427" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
@@ -15035,7 +15041,7 @@
         <v>1421</v>
       </c>
       <c r="G428" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
@@ -15058,7 +15064,7 @@
         <v>1421</v>
       </c>
       <c r="G429" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
@@ -15081,7 +15087,7 @@
         <v>1421</v>
       </c>
       <c r="G430" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
@@ -15104,7 +15110,7 @@
         <v>1421</v>
       </c>
       <c r="G431" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
@@ -15127,7 +15133,7 @@
         <v>1421</v>
       </c>
       <c r="G432" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
@@ -15150,7 +15156,7 @@
         <v>1421</v>
       </c>
       <c r="G433" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
@@ -15173,7 +15179,7 @@
         <v>1421</v>
       </c>
       <c r="G434" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
@@ -15196,7 +15202,7 @@
         <v>1421</v>
       </c>
       <c r="G435" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
@@ -15219,7 +15225,7 @@
         <v>1421</v>
       </c>
       <c r="G436" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
@@ -15242,7 +15248,7 @@
         <v>1421</v>
       </c>
       <c r="G437" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
@@ -15265,7 +15271,7 @@
         <v>1421</v>
       </c>
       <c r="G438" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
@@ -15288,7 +15294,7 @@
         <v>1421</v>
       </c>
       <c r="G439" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
@@ -15311,7 +15317,7 @@
         <v>1421</v>
       </c>
       <c r="G440" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
@@ -15334,7 +15340,7 @@
         <v>1421</v>
       </c>
       <c r="G441" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
@@ -15357,7 +15363,7 @@
         <v>1421</v>
       </c>
       <c r="G442" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
@@ -15380,7 +15386,7 @@
         <v>1421</v>
       </c>
       <c r="G443" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
@@ -15403,7 +15409,7 @@
         <v>1421</v>
       </c>
       <c r="G444" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
@@ -15426,7 +15432,7 @@
         <v>1421</v>
       </c>
       <c r="G445" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
@@ -15449,7 +15455,7 @@
         <v>1421</v>
       </c>
       <c r="G446" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.3">
@@ -15472,7 +15478,7 @@
         <v>1421</v>
       </c>
       <c r="G447" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
@@ -15495,7 +15501,7 @@
         <v>1421</v>
       </c>
       <c r="G448" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
@@ -15518,7 +15524,7 @@
         <v>1421</v>
       </c>
       <c r="G449" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
@@ -15541,7 +15547,7 @@
         <v>1421</v>
       </c>
       <c r="G450" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
@@ -15564,7 +15570,7 @@
         <v>1421</v>
       </c>
       <c r="G451" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.3">
@@ -15587,7 +15593,7 @@
         <v>1421</v>
       </c>
       <c r="G452" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.3">
@@ -15610,7 +15616,7 @@
         <v>1421</v>
       </c>
       <c r="G453" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
@@ -15633,7 +15639,7 @@
         <v>1421</v>
       </c>
       <c r="G454" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
@@ -15656,7 +15662,7 @@
         <v>1421</v>
       </c>
       <c r="G455" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
@@ -15679,7 +15685,7 @@
         <v>1421</v>
       </c>
       <c r="G456" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
@@ -15702,7 +15708,7 @@
         <v>1421</v>
       </c>
       <c r="G457" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
@@ -15725,7 +15731,7 @@
         <v>1421</v>
       </c>
       <c r="G458" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
@@ -15748,7 +15754,7 @@
         <v>1421</v>
       </c>
       <c r="G459" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
@@ -15771,7 +15777,7 @@
         <v>1421</v>
       </c>
       <c r="G460" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
@@ -15794,7 +15800,7 @@
         <v>1421</v>
       </c>
       <c r="G461" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
@@ -15817,7 +15823,7 @@
         <v>1421</v>
       </c>
       <c r="G462" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.3">
@@ -15840,7 +15846,7 @@
         <v>1421</v>
       </c>
       <c r="G463" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
@@ -15863,7 +15869,7 @@
         <v>1421</v>
       </c>
       <c r="G464" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.3">
@@ -15886,7 +15892,7 @@
         <v>1421</v>
       </c>
       <c r="G465" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.3">
@@ -15909,7 +15915,7 @@
         <v>1421</v>
       </c>
       <c r="G466" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.3">
@@ -15932,7 +15938,7 @@
         <v>1421</v>
       </c>
       <c r="G467" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.3">
@@ -15955,7 +15961,7 @@
         <v>1421</v>
       </c>
       <c r="G468" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.3">
@@ -15978,7 +15984,7 @@
         <v>1421</v>
       </c>
       <c r="G469" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.3">
@@ -16001,7 +16007,7 @@
         <v>1421</v>
       </c>
       <c r="G470" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.3">
@@ -16024,7 +16030,7 @@
         <v>1421</v>
       </c>
       <c r="G471" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.3">
@@ -16047,7 +16053,7 @@
         <v>1421</v>
       </c>
       <c r="G472" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.3">
@@ -16070,7 +16076,7 @@
         <v>1421</v>
       </c>
       <c r="G473" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.3">
@@ -16093,7 +16099,7 @@
         <v>1421</v>
       </c>
       <c r="G474" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.3">
@@ -16116,7 +16122,7 @@
         <v>1421</v>
       </c>
       <c r="G475" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.3">
@@ -16139,7 +16145,7 @@
         <v>1421</v>
       </c>
       <c r="G476" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.3">
@@ -16162,7 +16168,7 @@
         <v>1421</v>
       </c>
       <c r="G477" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.3">
@@ -16185,7 +16191,7 @@
         <v>1421</v>
       </c>
       <c r="G478" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.3">
@@ -16208,7 +16214,7 @@
         <v>1421</v>
       </c>
       <c r="G479" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.3">
@@ -16231,7 +16237,7 @@
         <v>1421</v>
       </c>
       <c r="G480" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.3">
@@ -16254,7 +16260,7 @@
         <v>1421</v>
       </c>
       <c r="G481" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.3">
@@ -16277,7 +16283,7 @@
         <v>1421</v>
       </c>
       <c r="G482" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.3">
@@ -16300,7 +16306,7 @@
         <v>1421</v>
       </c>
       <c r="G483" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.3">
@@ -16323,7 +16329,7 @@
         <v>1421</v>
       </c>
       <c r="G484" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.3">
@@ -16346,7 +16352,7 @@
         <v>1421</v>
       </c>
       <c r="G485" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.3">
@@ -16369,7 +16375,7 @@
         <v>1421</v>
       </c>
       <c r="G486" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.3">
@@ -16392,7 +16398,7 @@
         <v>1421</v>
       </c>
       <c r="G487" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.3">
@@ -16415,7 +16421,7 @@
         <v>1421</v>
       </c>
       <c r="G488" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.3">
@@ -16438,7 +16444,7 @@
         <v>1421</v>
       </c>
       <c r="G489" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.3">
@@ -16461,7 +16467,7 @@
         <v>1421</v>
       </c>
       <c r="G490" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.3">
@@ -16484,7 +16490,7 @@
         <v>1421</v>
       </c>
       <c r="G491" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.3">
@@ -16507,7 +16513,7 @@
         <v>1421</v>
       </c>
       <c r="G492" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.3">
@@ -16530,7 +16536,7 @@
         <v>1421</v>
       </c>
       <c r="G493" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.3">
@@ -16553,7 +16559,7 @@
         <v>1421</v>
       </c>
       <c r="G494" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.3">
@@ -16576,7 +16582,7 @@
         <v>1421</v>
       </c>
       <c r="G495" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.3">
@@ -16599,7 +16605,7 @@
         <v>1421</v>
       </c>
       <c r="G496" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
@@ -16622,7 +16628,7 @@
         <v>1421</v>
       </c>
       <c r="G497" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
@@ -16645,7 +16651,7 @@
         <v>1421</v>
       </c>
       <c r="G498" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
@@ -16668,7 +16674,7 @@
         <v>1421</v>
       </c>
       <c r="G499" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
@@ -16691,7 +16697,7 @@
         <v>1421</v>
       </c>
       <c r="G500" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
@@ -16714,7 +16720,7 @@
         <v>1421</v>
       </c>
       <c r="G501" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
@@ -16737,7 +16743,7 @@
         <v>1421</v>
       </c>
       <c r="G502" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
@@ -16760,7 +16766,7 @@
         <v>1421</v>
       </c>
       <c r="G503" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
@@ -16783,7 +16789,7 @@
         <v>1421</v>
       </c>
       <c r="G504" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
@@ -16806,7 +16812,7 @@
         <v>1421</v>
       </c>
       <c r="G505" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
@@ -16829,7 +16835,7 @@
         <v>1421</v>
       </c>
       <c r="G506" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
@@ -16852,7 +16858,7 @@
         <v>1421</v>
       </c>
       <c r="G507" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
@@ -16875,7 +16881,7 @@
         <v>1421</v>
       </c>
       <c r="G508" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
@@ -16898,7 +16904,7 @@
         <v>1421</v>
       </c>
       <c r="G509" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
@@ -16921,7 +16927,7 @@
         <v>1421</v>
       </c>
       <c r="G510" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
@@ -16944,7 +16950,7 @@
         <v>1421</v>
       </c>
       <c r="G511" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
@@ -16967,7 +16973,7 @@
         <v>1421</v>
       </c>
       <c r="G512" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
@@ -16990,7 +16996,7 @@
         <v>1421</v>
       </c>
       <c r="G513" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
@@ -17013,7 +17019,7 @@
         <v>1421</v>
       </c>
       <c r="G514" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
@@ -17036,7 +17042,7 @@
         <v>1421</v>
       </c>
       <c r="G515" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
@@ -17059,7 +17065,7 @@
         <v>1421</v>
       </c>
       <c r="G516" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
@@ -17082,7 +17088,7 @@
         <v>1421</v>
       </c>
       <c r="G517" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
@@ -17105,7 +17111,7 @@
         <v>1421</v>
       </c>
       <c r="G518" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
@@ -17128,7 +17134,7 @@
         <v>1421</v>
       </c>
       <c r="G519" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
@@ -17151,7 +17157,7 @@
         <v>1421</v>
       </c>
       <c r="G520" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
@@ -17174,7 +17180,7 @@
         <v>1421</v>
       </c>
       <c r="G521" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
@@ -17197,7 +17203,7 @@
         <v>1421</v>
       </c>
       <c r="G522" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
@@ -17220,7 +17226,7 @@
         <v>1421</v>
       </c>
       <c r="G523" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
@@ -17243,7 +17249,7 @@
         <v>1421</v>
       </c>
       <c r="G524" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
@@ -17266,7 +17272,7 @@
         <v>1421</v>
       </c>
       <c r="G525" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
@@ -17289,7 +17295,7 @@
         <v>1421</v>
       </c>
       <c r="G526" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
@@ -17312,7 +17318,7 @@
         <v>1421</v>
       </c>
       <c r="G527" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
@@ -17335,7 +17341,7 @@
         <v>1421</v>
       </c>
       <c r="G528" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.3">
@@ -17358,7 +17364,7 @@
         <v>1421</v>
       </c>
       <c r="G529" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.3">
@@ -17381,7 +17387,7 @@
         <v>1421</v>
       </c>
       <c r="G530" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.3">
@@ -17404,7 +17410,7 @@
         <v>1421</v>
       </c>
       <c r="G531" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.3">
@@ -17427,7 +17433,7 @@
         <v>1421</v>
       </c>
       <c r="G532" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.3">
@@ -17450,7 +17456,7 @@
         <v>1421</v>
       </c>
       <c r="G533" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.3">
@@ -17473,7 +17479,7 @@
         <v>1421</v>
       </c>
       <c r="G534" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.3">
@@ -17496,7 +17502,7 @@
         <v>1421</v>
       </c>
       <c r="G535" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.3">
@@ -17519,7 +17525,7 @@
         <v>1421</v>
       </c>
       <c r="G536" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.3">
@@ -17542,7 +17548,7 @@
         <v>1421</v>
       </c>
       <c r="G537" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.3">
@@ -17565,7 +17571,7 @@
         <v>1421</v>
       </c>
       <c r="G538" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.3">
@@ -17588,7 +17594,7 @@
         <v>1421</v>
       </c>
       <c r="G539" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.3">
@@ -17611,7 +17617,7 @@
         <v>1421</v>
       </c>
       <c r="G540" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.3">
@@ -17634,7 +17640,7 @@
         <v>1421</v>
       </c>
       <c r="G541" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.3">
@@ -17657,7 +17663,7 @@
         <v>1421</v>
       </c>
       <c r="G542" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.3">
@@ -17680,7 +17686,7 @@
         <v>1421</v>
       </c>
       <c r="G543" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.3">
@@ -17703,7 +17709,7 @@
         <v>1421</v>
       </c>
       <c r="G544" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
@@ -17726,7 +17732,7 @@
         <v>1421</v>
       </c>
       <c r="G545" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
@@ -17749,7 +17755,7 @@
         <v>1421</v>
       </c>
       <c r="G546" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
@@ -17772,7 +17778,7 @@
         <v>1421</v>
       </c>
       <c r="G547" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.3">
@@ -17795,7 +17801,7 @@
         <v>1421</v>
       </c>
       <c r="G548" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.3">
@@ -17818,7 +17824,7 @@
         <v>1421</v>
       </c>
       <c r="G549" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.3">
@@ -17841,7 +17847,7 @@
         <v>1421</v>
       </c>
       <c r="G550" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.3">
@@ -17864,7 +17870,7 @@
         <v>1421</v>
       </c>
       <c r="G551" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.3">
@@ -17887,7 +17893,7 @@
         <v>1421</v>
       </c>
       <c r="G552" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.3">
@@ -17910,7 +17916,7 @@
         <v>1421</v>
       </c>
       <c r="G553" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.3">
@@ -17933,7 +17939,7 @@
         <v>1421</v>
       </c>
       <c r="G554" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.3">
@@ -17956,7 +17962,7 @@
         <v>1421</v>
       </c>
       <c r="G555" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.3">
@@ -17979,7 +17985,7 @@
         <v>1421</v>
       </c>
       <c r="G556" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.3">
@@ -18002,7 +18008,7 @@
         <v>1421</v>
       </c>
       <c r="G557" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.3">
@@ -18025,7 +18031,7 @@
         <v>1421</v>
       </c>
       <c r="G558" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.3">
@@ -18048,7 +18054,7 @@
         <v>1421</v>
       </c>
       <c r="G559" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.3">
@@ -18071,7 +18077,7 @@
         <v>1421</v>
       </c>
       <c r="G560" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.3">
@@ -18094,7 +18100,7 @@
         <v>1421</v>
       </c>
       <c r="G561" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.3">
@@ -18117,7 +18123,7 @@
         <v>1421</v>
       </c>
       <c r="G562" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.3">
@@ -18140,7 +18146,7 @@
         <v>1421</v>
       </c>
       <c r="G563" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.3">
@@ -18163,7 +18169,7 @@
         <v>1421</v>
       </c>
       <c r="G564" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.3">
@@ -18186,7 +18192,7 @@
         <v>1421</v>
       </c>
       <c r="G565" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.3">
@@ -18209,7 +18215,7 @@
         <v>1421</v>
       </c>
       <c r="G566" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.3">
@@ -18232,7 +18238,7 @@
         <v>1421</v>
       </c>
       <c r="G567" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.3">
@@ -18255,7 +18261,7 @@
         <v>1421</v>
       </c>
       <c r="G568" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.3">
@@ -18278,7 +18284,7 @@
         <v>1421</v>
       </c>
       <c r="G569" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.3">
@@ -18301,7 +18307,7 @@
         <v>1421</v>
       </c>
       <c r="G570" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.3">
@@ -18324,7 +18330,7 @@
         <v>1421</v>
       </c>
       <c r="G571" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.3">
@@ -18347,7 +18353,7 @@
         <v>1421</v>
       </c>
       <c r="G572" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.3">
@@ -18370,7 +18376,7 @@
         <v>1421</v>
       </c>
       <c r="G573" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.3">
@@ -18393,7 +18399,7 @@
         <v>1421</v>
       </c>
       <c r="G574" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.3">
@@ -18416,7 +18422,7 @@
         <v>1421</v>
       </c>
       <c r="G575" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.3">
@@ -18439,7 +18445,7 @@
         <v>1421</v>
       </c>
       <c r="G576" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.3">
@@ -18462,7 +18468,7 @@
         <v>1421</v>
       </c>
       <c r="G577" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.3">
@@ -18485,7 +18491,7 @@
         <v>1421</v>
       </c>
       <c r="G578" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.3">
@@ -18508,7 +18514,7 @@
         <v>1421</v>
       </c>
       <c r="G579" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.3">
@@ -18531,7 +18537,7 @@
         <v>1421</v>
       </c>
       <c r="G580" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.3">
@@ -18554,7 +18560,7 @@
         <v>1421</v>
       </c>
       <c r="G581" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.3">
@@ -18577,7 +18583,7 @@
         <v>1421</v>
       </c>
       <c r="G582" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
@@ -18600,7 +18606,7 @@
         <v>1421</v>
       </c>
       <c r="G583" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.3">
@@ -18623,7 +18629,7 @@
         <v>1421</v>
       </c>
       <c r="G584" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.3">
@@ -18646,7 +18652,7 @@
         <v>1421</v>
       </c>
       <c r="G585" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.3">
@@ -18669,7 +18675,7 @@
         <v>1421</v>
       </c>
       <c r="G586" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.3">
@@ -18692,7 +18698,7 @@
         <v>1421</v>
       </c>
       <c r="G587" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.3">
@@ -18715,7 +18721,7 @@
         <v>1421</v>
       </c>
       <c r="G588" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.3">
@@ -18738,7 +18744,7 @@
         <v>1421</v>
       </c>
       <c r="G589" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.3">
@@ -18761,7 +18767,7 @@
         <v>1421</v>
       </c>
       <c r="G590" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.3">
@@ -18784,7 +18790,7 @@
         <v>1421</v>
       </c>
       <c r="G591" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.3">
@@ -18807,7 +18813,7 @@
         <v>1421</v>
       </c>
       <c r="G592" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
@@ -18830,7 +18836,7 @@
         <v>1421</v>
       </c>
       <c r="G593" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
@@ -18853,7 +18859,7 @@
         <v>1421</v>
       </c>
       <c r="G594" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.3">
@@ -18876,7 +18882,7 @@
         <v>1421</v>
       </c>
       <c r="G595" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
@@ -18899,7 +18905,7 @@
         <v>1421</v>
       </c>
       <c r="G596" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.3">
@@ -18922,7 +18928,7 @@
         <v>1421</v>
       </c>
       <c r="G597" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.3">
@@ -18945,7 +18951,7 @@
         <v>1421</v>
       </c>
       <c r="G598" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.3">
@@ -18968,7 +18974,7 @@
         <v>1421</v>
       </c>
       <c r="G599" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.3">
@@ -18991,7 +18997,7 @@
         <v>1421</v>
       </c>
       <c r="G600" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.3">
@@ -19014,7 +19020,7 @@
         <v>1421</v>
       </c>
       <c r="G601" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.3">
@@ -19037,7 +19043,7 @@
         <v>1421</v>
       </c>
       <c r="G602" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.3">
@@ -19060,7 +19066,7 @@
         <v>1421</v>
       </c>
       <c r="G603" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.3">
@@ -19083,7 +19089,7 @@
         <v>1421</v>
       </c>
       <c r="G604" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.3">
@@ -19106,7 +19112,7 @@
         <v>1421</v>
       </c>
       <c r="G605" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.3">
@@ -19129,7 +19135,7 @@
         <v>1421</v>
       </c>
       <c r="G606" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.3">
@@ -19152,7 +19158,7 @@
         <v>1421</v>
       </c>
       <c r="G607" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.3">
@@ -19175,7 +19181,7 @@
         <v>1421</v>
       </c>
       <c r="G608" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.3">
@@ -19198,7 +19204,7 @@
         <v>1421</v>
       </c>
       <c r="G609" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.3">
@@ -19221,7 +19227,7 @@
         <v>1421</v>
       </c>
       <c r="G610" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.3">
@@ -19244,7 +19250,7 @@
         <v>1421</v>
       </c>
       <c r="G611" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.3">
@@ -19267,7 +19273,7 @@
         <v>1421</v>
       </c>
       <c r="G612" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.3">
@@ -19290,7 +19296,7 @@
         <v>1421</v>
       </c>
       <c r="G613" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.3">
@@ -19313,7 +19319,7 @@
         <v>1421</v>
       </c>
       <c r="G614" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.3">
@@ -19336,7 +19342,7 @@
         <v>1421</v>
       </c>
       <c r="G615" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.3">
@@ -19359,7 +19365,7 @@
         <v>1421</v>
       </c>
       <c r="G616" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.3">
@@ -19382,7 +19388,7 @@
         <v>1421</v>
       </c>
       <c r="G617" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.3">
@@ -19405,7 +19411,7 @@
         <v>1421</v>
       </c>
       <c r="G618" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.3">
@@ -19428,7 +19434,7 @@
         <v>1421</v>
       </c>
       <c r="G619" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.3">
@@ -19451,7 +19457,7 @@
         <v>1421</v>
       </c>
       <c r="G620" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.3">
@@ -19474,7 +19480,7 @@
         <v>1421</v>
       </c>
       <c r="G621" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.3">
@@ -19497,7 +19503,7 @@
         <v>1421</v>
       </c>
       <c r="G622" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.3">
@@ -19520,7 +19526,7 @@
         <v>1421</v>
       </c>
       <c r="G623" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.3">
@@ -19543,7 +19549,7 @@
         <v>1421</v>
       </c>
       <c r="G624" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.3">
@@ -19566,7 +19572,7 @@
         <v>1421</v>
       </c>
       <c r="G625" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.3">
@@ -19589,7 +19595,7 @@
         <v>1421</v>
       </c>
       <c r="G626" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.3">
@@ -19612,7 +19618,7 @@
         <v>1421</v>
       </c>
       <c r="G627" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.3">
@@ -19635,7 +19641,7 @@
         <v>1421</v>
       </c>
       <c r="G628" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.3">
@@ -19658,7 +19664,7 @@
         <v>1421</v>
       </c>
       <c r="G629" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.3">
@@ -19681,7 +19687,7 @@
         <v>1421</v>
       </c>
       <c r="G630" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.3">
@@ -19704,7 +19710,7 @@
         <v>1421</v>
       </c>
       <c r="G631" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.3">
@@ -19727,7 +19733,7 @@
         <v>1421</v>
       </c>
       <c r="G632" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.3">
@@ -19750,7 +19756,7 @@
         <v>1421</v>
       </c>
       <c r="G633" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.3">
@@ -19773,7 +19779,7 @@
         <v>1421</v>
       </c>
       <c r="G634" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.3">
@@ -19796,7 +19802,7 @@
         <v>1421</v>
       </c>
       <c r="G635" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.3">
@@ -19819,7 +19825,7 @@
         <v>1421</v>
       </c>
       <c r="G636" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.3">
@@ -19842,7 +19848,7 @@
         <v>1421</v>
       </c>
       <c r="G637" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.3">
@@ -19865,7 +19871,7 @@
         <v>1421</v>
       </c>
       <c r="G638" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.3">
@@ -19888,7 +19894,7 @@
         <v>1421</v>
       </c>
       <c r="G639" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.3">
@@ -19911,7 +19917,7 @@
         <v>1421</v>
       </c>
       <c r="G640" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.3">
@@ -19934,7 +19940,7 @@
         <v>1421</v>
       </c>
       <c r="G641" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.3">
@@ -19957,7 +19963,7 @@
         <v>1421</v>
       </c>
       <c r="G642" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.3">
@@ -19980,7 +19986,7 @@
         <v>1421</v>
       </c>
       <c r="G643" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.3">
@@ -20003,7 +20009,7 @@
         <v>1421</v>
       </c>
       <c r="G644" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.3">
@@ -20026,7 +20032,7 @@
         <v>1421</v>
       </c>
       <c r="G645" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.3">
@@ -20049,7 +20055,7 @@
         <v>1421</v>
       </c>
       <c r="G646" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.3">
@@ -20072,7 +20078,7 @@
         <v>1421</v>
       </c>
       <c r="G647" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.3">
@@ -20095,7 +20101,7 @@
         <v>1421</v>
       </c>
       <c r="G648" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.3">
@@ -20118,7 +20124,7 @@
         <v>1421</v>
       </c>
       <c r="G649" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.3">
@@ -20141,7 +20147,7 @@
         <v>1421</v>
       </c>
       <c r="G650" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.3">
@@ -20164,7 +20170,7 @@
         <v>1421</v>
       </c>
       <c r="G651" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.3">
@@ -20187,7 +20193,7 @@
         <v>1421</v>
       </c>
       <c r="G652" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.3">
@@ -20210,7 +20216,7 @@
         <v>1421</v>
       </c>
       <c r="G653" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.3">
@@ -20233,7 +20239,7 @@
         <v>1421</v>
       </c>
       <c r="G654" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.3">
@@ -20256,7 +20262,7 @@
         <v>1421</v>
       </c>
       <c r="G655" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.3">
@@ -20279,7 +20285,7 @@
         <v>1421</v>
       </c>
       <c r="G656" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.3">
@@ -20302,7 +20308,7 @@
         <v>1421</v>
       </c>
       <c r="G657" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.3">
@@ -20325,7 +20331,7 @@
         <v>1421</v>
       </c>
       <c r="G658" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.3">
@@ -20348,7 +20354,7 @@
         <v>1421</v>
       </c>
       <c r="G659" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.3">
@@ -20371,7 +20377,7 @@
         <v>1421</v>
       </c>
       <c r="G660" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.3">
@@ -20394,7 +20400,7 @@
         <v>1421</v>
       </c>
       <c r="G661" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.3">
@@ -20417,7 +20423,7 @@
         <v>1421</v>
       </c>
       <c r="G662" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.3">
@@ -20440,7 +20446,7 @@
         <v>1421</v>
       </c>
       <c r="G663" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.3">
@@ -20463,7 +20469,7 @@
         <v>1421</v>
       </c>
       <c r="G664" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.3">
@@ -20486,7 +20492,7 @@
         <v>1421</v>
       </c>
       <c r="G665" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.3">
@@ -20509,7 +20515,7 @@
         <v>1421</v>
       </c>
       <c r="G666" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.3">
@@ -20532,7 +20538,7 @@
         <v>1421</v>
       </c>
       <c r="G667" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.3">
@@ -20555,7 +20561,7 @@
         <v>1421</v>
       </c>
       <c r="G668" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.3">
@@ -20578,7 +20584,7 @@
         <v>1421</v>
       </c>
       <c r="G669" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.3">
@@ -20601,7 +20607,7 @@
         <v>1421</v>
       </c>
       <c r="G670" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.3">
@@ -20624,7 +20630,7 @@
         <v>1421</v>
       </c>
       <c r="G671" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.3">
@@ -20647,7 +20653,7 @@
         <v>1421</v>
       </c>
       <c r="G672" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.3">
@@ -20670,7 +20676,7 @@
         <v>1421</v>
       </c>
       <c r="G673" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.3">
@@ -20693,7 +20699,7 @@
         <v>1421</v>
       </c>
       <c r="G674" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.3">
@@ -20716,7 +20722,7 @@
         <v>1421</v>
       </c>
       <c r="G675" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.3">
@@ -20739,7 +20745,7 @@
         <v>1421</v>
       </c>
       <c r="G676" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.3">
@@ -20762,7 +20768,7 @@
         <v>1421</v>
       </c>
       <c r="G677" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.3">
@@ -20785,7 +20791,7 @@
         <v>1421</v>
       </c>
       <c r="G678" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.3">
@@ -20808,7 +20814,7 @@
         <v>1421</v>
       </c>
       <c r="G679" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.3">
@@ -20831,7 +20837,7 @@
         <v>1421</v>
       </c>
       <c r="G680" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.3">
@@ -20854,7 +20860,7 @@
         <v>1421</v>
       </c>
       <c r="G681" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.3">
@@ -20877,7 +20883,7 @@
         <v>1421</v>
       </c>
       <c r="G682" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.3">
@@ -20900,7 +20906,7 @@
         <v>1421</v>
       </c>
       <c r="G683" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.3">
@@ -20923,7 +20929,7 @@
         <v>1421</v>
       </c>
       <c r="G684" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.3">
@@ -20946,7 +20952,7 @@
         <v>1421</v>
       </c>
       <c r="G685" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.3">
@@ -20969,7 +20975,7 @@
         <v>1421</v>
       </c>
       <c r="G686" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.3">
@@ -20992,7 +20998,7 @@
         <v>1421</v>
       </c>
       <c r="G687" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.3">
@@ -21015,7 +21021,7 @@
         <v>1421</v>
       </c>
       <c r="G688" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.3">
@@ -21038,7 +21044,7 @@
         <v>1421</v>
       </c>
       <c r="G689" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.3">
@@ -21061,7 +21067,7 @@
         <v>1421</v>
       </c>
       <c r="G690" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.3">
@@ -21084,7 +21090,7 @@
         <v>1421</v>
       </c>
       <c r="G691" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.3">
@@ -21107,7 +21113,7 @@
         <v>1421</v>
       </c>
       <c r="G692" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.3">
@@ -21130,7 +21136,7 @@
         <v>1421</v>
       </c>
       <c r="G693" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.3">
@@ -21153,7 +21159,7 @@
         <v>1421</v>
       </c>
       <c r="G694" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.3">
@@ -21176,7 +21182,7 @@
         <v>1421</v>
       </c>
       <c r="G695" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.3">
@@ -21199,7 +21205,7 @@
         <v>1421</v>
       </c>
       <c r="G696" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.3">
@@ -21222,7 +21228,7 @@
         <v>1421</v>
       </c>
       <c r="G697" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.3">
@@ -21245,7 +21251,7 @@
         <v>1421</v>
       </c>
       <c r="G698" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.3">
@@ -21268,7 +21274,7 @@
         <v>1421</v>
       </c>
       <c r="G699" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.3">
@@ -21291,7 +21297,7 @@
         <v>1421</v>
       </c>
       <c r="G700" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.3">
@@ -21314,7 +21320,7 @@
         <v>1421</v>
       </c>
       <c r="G701" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.3">
@@ -21337,7 +21343,7 @@
         <v>1421</v>
       </c>
       <c r="G702" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.3">
@@ -21360,7 +21366,7 @@
         <v>1421</v>
       </c>
       <c r="G703" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.3">
@@ -21383,7 +21389,7 @@
         <v>1421</v>
       </c>
       <c r="G704" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.3">
@@ -21406,7 +21412,7 @@
         <v>1421</v>
       </c>
       <c r="G705" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.3">
@@ -21429,7 +21435,7 @@
         <v>1421</v>
       </c>
       <c r="G706" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.3">
@@ -21452,7 +21458,7 @@
         <v>1421</v>
       </c>
       <c r="G707" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.3">
@@ -21475,7 +21481,7 @@
         <v>1421</v>
       </c>
       <c r="G708" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.3">
@@ -21498,7 +21504,7 @@
         <v>1421</v>
       </c>
       <c r="G709" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.3">
@@ -21521,7 +21527,7 @@
         <v>1421</v>
       </c>
       <c r="G710" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.3">
@@ -21544,7 +21550,7 @@
         <v>1421</v>
       </c>
       <c r="G711" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.3">
@@ -21567,7 +21573,7 @@
         <v>1421</v>
       </c>
       <c r="G712" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.3">
@@ -21590,7 +21596,7 @@
         <v>1421</v>
       </c>
       <c r="G713" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.3">
@@ -21613,7 +21619,7 @@
         <v>1421</v>
       </c>
       <c r="G714" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.3">
@@ -21636,7 +21642,7 @@
         <v>1421</v>
       </c>
       <c r="G715" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.3">
@@ -21659,7 +21665,7 @@
         <v>1421</v>
       </c>
       <c r="G716" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.3">
@@ -21682,7 +21688,7 @@
         <v>1421</v>
       </c>
       <c r="G717" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.3">
@@ -21705,7 +21711,7 @@
         <v>1421</v>
       </c>
       <c r="G718" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.3">
@@ -21728,7 +21734,7 @@
         <v>1421</v>
       </c>
       <c r="G719" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.3">
@@ -21751,7 +21757,7 @@
         <v>1421</v>
       </c>
       <c r="G720" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.3">
@@ -21774,7 +21780,7 @@
         <v>1421</v>
       </c>
       <c r="G721" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.3">
@@ -21797,7 +21803,7 @@
         <v>1421</v>
       </c>
       <c r="G722" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.3">
@@ -21820,7 +21826,7 @@
         <v>1421</v>
       </c>
       <c r="G723" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.3">
@@ -21843,7 +21849,7 @@
         <v>1421</v>
       </c>
       <c r="G724" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.3">
@@ -21866,7 +21872,7 @@
         <v>1421</v>
       </c>
       <c r="G725" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.3">
@@ -21889,7 +21895,7 @@
         <v>1421</v>
       </c>
       <c r="G726" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.3">
@@ -21912,7 +21918,7 @@
         <v>1421</v>
       </c>
       <c r="G727" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.3">
@@ -21935,7 +21941,7 @@
         <v>1421</v>
       </c>
       <c r="G728" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.3">
@@ -21958,7 +21964,7 @@
         <v>1421</v>
       </c>
       <c r="G729" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.3">
@@ -21981,7 +21987,7 @@
         <v>1421</v>
       </c>
       <c r="G730" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.3">
@@ -22004,7 +22010,7 @@
         <v>1421</v>
       </c>
       <c r="G731" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.3">
@@ -22027,7 +22033,7 @@
         <v>1421</v>
       </c>
       <c r="G732" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.3">
@@ -22050,7 +22056,7 @@
         <v>1421</v>
       </c>
       <c r="G733" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.3">
@@ -22073,7 +22079,7 @@
         <v>1421</v>
       </c>
       <c r="G734" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.3">
@@ -22096,7 +22102,7 @@
         <v>1421</v>
       </c>
       <c r="G735" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.3">
@@ -22119,7 +22125,7 @@
         <v>1421</v>
       </c>
       <c r="G736" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="737" spans="1:7" x14ac:dyDescent="0.3">
@@ -22142,7 +22148,7 @@
         <v>1421</v>
       </c>
       <c r="G737" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.3">
@@ -22165,7 +22171,7 @@
         <v>1421</v>
       </c>
       <c r="G738" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.3">
@@ -22188,7 +22194,7 @@
         <v>1421</v>
       </c>
       <c r="G739" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.3">
@@ -22211,7 +22217,7 @@
         <v>1421</v>
       </c>
       <c r="G740" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.3">
@@ -22234,7 +22240,7 @@
         <v>1421</v>
       </c>
       <c r="G741" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="742" spans="1:7" x14ac:dyDescent="0.3">
@@ -22257,7 +22263,7 @@
         <v>1421</v>
       </c>
       <c r="G742" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.3">
@@ -22280,7 +22286,7 @@
         <v>1421</v>
       </c>
       <c r="G743" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.3">
@@ -22303,7 +22309,7 @@
         <v>1421</v>
       </c>
       <c r="G744" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.3">
@@ -22326,7 +22332,7 @@
         <v>1421</v>
       </c>
       <c r="G745" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.3">
@@ -22349,7 +22355,7 @@
         <v>1421</v>
       </c>
       <c r="G746" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.3">
@@ -22372,7 +22378,7 @@
         <v>1421</v>
       </c>
       <c r="G747" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.3">
@@ -22395,7 +22401,7 @@
         <v>1421</v>
       </c>
       <c r="G748" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="749" spans="1:7" x14ac:dyDescent="0.3">
@@ -22417,9 +22423,7 @@
       <c r="F749" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="G749" s="14" t="s">
-        <v>1462</v>
-      </c>
+      <c r="G749" s="14"/>
     </row>
     <row r="750" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A750" s="12">
@@ -22441,7 +22445,7 @@
         <v>1421</v>
       </c>
       <c r="G750" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.3">
@@ -22464,7 +22468,7 @@
         <v>1421</v>
       </c>
       <c r="G751" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="752" spans="1:7" x14ac:dyDescent="0.3">
@@ -22487,7 +22491,7 @@
         <v>1421</v>
       </c>
       <c r="G752" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="753" spans="1:7" x14ac:dyDescent="0.3">
@@ -22510,7 +22514,7 @@
         <v>1421</v>
       </c>
       <c r="G753" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="754" spans="1:7" x14ac:dyDescent="0.3">
@@ -22533,7 +22537,7 @@
         <v>1421</v>
       </c>
       <c r="G754" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.3">
@@ -22556,7 +22560,7 @@
         <v>1421</v>
       </c>
       <c r="G755" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="756" spans="1:7" x14ac:dyDescent="0.3">
@@ -22579,7 +22583,7 @@
         <v>1421</v>
       </c>
       <c r="G756" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="757" spans="1:7" x14ac:dyDescent="0.3">
@@ -22602,7 +22606,7 @@
         <v>1421</v>
       </c>
       <c r="G757" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="758" spans="1:7" x14ac:dyDescent="0.3">
@@ -22625,7 +22629,7 @@
         <v>1421</v>
       </c>
       <c r="G758" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.3">
@@ -22648,7 +22652,7 @@
         <v>1421</v>
       </c>
       <c r="G759" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="760" spans="1:7" x14ac:dyDescent="0.3">
@@ -22671,7 +22675,7 @@
         <v>1421</v>
       </c>
       <c r="G760" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.3">
@@ -22694,7 +22698,7 @@
         <v>1421</v>
       </c>
       <c r="G761" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="762" spans="1:7" x14ac:dyDescent="0.3">
@@ -22717,7 +22721,7 @@
         <v>1421</v>
       </c>
       <c r="G762" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.3">
@@ -22739,9 +22743,7 @@
       <c r="F763" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="G763" s="14" t="s">
-        <v>1462</v>
-      </c>
+      <c r="G763" s="14"/>
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A764" s="12">
@@ -22763,7 +22765,7 @@
         <v>1421</v>
       </c>
       <c r="G764" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.3">
@@ -22786,7 +22788,7 @@
         <v>1421</v>
       </c>
       <c r="G765" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="766" spans="1:7" x14ac:dyDescent="0.3">
@@ -22809,7 +22811,7 @@
         <v>1421</v>
       </c>
       <c r="G766" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="767" spans="1:7" x14ac:dyDescent="0.3">
@@ -22832,7 +22834,7 @@
         <v>1421</v>
       </c>
       <c r="G767" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="768" spans="1:7" x14ac:dyDescent="0.3">
@@ -22855,7 +22857,7 @@
         <v>1421</v>
       </c>
       <c r="G768" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="769" spans="1:7" x14ac:dyDescent="0.3">
@@ -22878,7 +22880,7 @@
         <v>1421</v>
       </c>
       <c r="G769" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.3">
@@ -22901,7 +22903,7 @@
         <v>1421</v>
       </c>
       <c r="G770" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="771" spans="1:7" x14ac:dyDescent="0.3">
@@ -22924,7 +22926,7 @@
         <v>1421</v>
       </c>
       <c r="G771" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="772" spans="1:7" x14ac:dyDescent="0.3">
@@ -22947,7 +22949,7 @@
         <v>1421</v>
       </c>
       <c r="G772" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="773" spans="1:7" x14ac:dyDescent="0.3">
@@ -22970,7 +22972,7 @@
         <v>1421</v>
       </c>
       <c r="G773" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.3">
@@ -22992,9 +22994,7 @@
       <c r="F774" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="G774" s="14" t="s">
-        <v>1462</v>
-      </c>
+      <c r="G774" s="14"/>
     </row>
     <row r="775" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A775" s="2">
@@ -23016,7 +23016,7 @@
         <v>1421</v>
       </c>
       <c r="G775" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="776" spans="1:7" x14ac:dyDescent="0.3">
@@ -23039,7 +23039,7 @@
         <v>1421</v>
       </c>
       <c r="G776" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="777" spans="1:7" x14ac:dyDescent="0.3">
@@ -23062,7 +23062,7 @@
         <v>1421</v>
       </c>
       <c r="G777" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.3">
@@ -23085,7 +23085,7 @@
         <v>1421</v>
       </c>
       <c r="G778" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="779" spans="1:7" x14ac:dyDescent="0.3">
@@ -23108,7 +23108,7 @@
         <v>1421</v>
       </c>
       <c r="G779" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="780" spans="1:7" x14ac:dyDescent="0.3">
@@ -23131,7 +23131,7 @@
         <v>1421</v>
       </c>
       <c r="G780" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.3">
@@ -23154,7 +23154,7 @@
         <v>1421</v>
       </c>
       <c r="G781" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="782" spans="1:7" x14ac:dyDescent="0.3">
@@ -23177,7 +23177,7 @@
         <v>1421</v>
       </c>
       <c r="G782" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.3">
@@ -23200,7 +23200,7 @@
         <v>1421</v>
       </c>
       <c r="G783" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.3">
@@ -23223,7 +23223,7 @@
         <v>1421</v>
       </c>
       <c r="G784" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="785" spans="1:7" x14ac:dyDescent="0.3">
@@ -23246,7 +23246,7 @@
         <v>1421</v>
       </c>
       <c r="G785" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="786" spans="1:7" x14ac:dyDescent="0.3">
@@ -23269,7 +23269,7 @@
         <v>1421</v>
       </c>
       <c r="G786" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="787" spans="1:7" x14ac:dyDescent="0.3">
@@ -23292,7 +23292,7 @@
         <v>1421</v>
       </c>
       <c r="G787" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.3">
@@ -23315,7 +23315,7 @@
         <v>1421</v>
       </c>
       <c r="G788" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.3">
@@ -23338,7 +23338,7 @@
         <v>1421</v>
       </c>
       <c r="G789" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="790" spans="1:7" x14ac:dyDescent="0.3">
@@ -23361,7 +23361,7 @@
         <v>1421</v>
       </c>
       <c r="G790" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="791" spans="1:7" x14ac:dyDescent="0.3">
@@ -23384,7 +23384,7 @@
         <v>1421</v>
       </c>
       <c r="G791" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="792" spans="1:7" x14ac:dyDescent="0.3">
@@ -23407,7 +23407,7 @@
         <v>1421</v>
       </c>
       <c r="G792" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.3">
@@ -23430,7 +23430,7 @@
         <v>1421</v>
       </c>
       <c r="G793" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="794" spans="1:7" x14ac:dyDescent="0.3">
@@ -23453,7 +23453,7 @@
         <v>1421</v>
       </c>
       <c r="G794" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="795" spans="1:7" x14ac:dyDescent="0.3">
@@ -23476,7 +23476,7 @@
         <v>1421</v>
       </c>
       <c r="G795" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="796" spans="1:7" x14ac:dyDescent="0.3">
@@ -23499,7 +23499,7 @@
         <v>1421</v>
       </c>
       <c r="G796" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="797" spans="1:7" x14ac:dyDescent="0.3">
@@ -23522,7 +23522,7 @@
         <v>1421</v>
       </c>
       <c r="G797" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="798" spans="1:7" x14ac:dyDescent="0.3">
@@ -23545,7 +23545,7 @@
         <v>1421</v>
       </c>
       <c r="G798" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="799" spans="1:7" x14ac:dyDescent="0.3">
@@ -23568,7 +23568,7 @@
         <v>1421</v>
       </c>
       <c r="G799" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="800" spans="1:7" x14ac:dyDescent="0.3">
@@ -23590,9 +23590,7 @@
       <c r="F800" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="G800" s="14" t="s">
-        <v>1462</v>
-      </c>
+      <c r="G800" s="14"/>
     </row>
     <row r="801" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A801" s="2">
@@ -23613,9 +23611,7 @@
       <c r="F801" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="G801" s="14" t="s">
-        <v>1462</v>
-      </c>
+      <c r="G801" s="14"/>
     </row>
     <row r="802" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A802" s="12">
@@ -23637,7 +23633,7 @@
         <v>1421</v>
       </c>
       <c r="G802" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="803" spans="1:7" x14ac:dyDescent="0.3">
@@ -23660,7 +23656,7 @@
         <v>1421</v>
       </c>
       <c r="G803" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="804" spans="1:7" x14ac:dyDescent="0.3">
@@ -23683,7 +23679,7 @@
         <v>1421</v>
       </c>
       <c r="G804" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="805" spans="1:7" x14ac:dyDescent="0.3">
@@ -23706,7 +23702,7 @@
         <v>1421</v>
       </c>
       <c r="G805" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="806" spans="1:7" x14ac:dyDescent="0.3">
@@ -23729,7 +23725,7 @@
         <v>1421</v>
       </c>
       <c r="G806" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="807" spans="1:7" x14ac:dyDescent="0.3">
@@ -23752,7 +23748,7 @@
         <v>1421</v>
       </c>
       <c r="G807" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="808" spans="1:7" x14ac:dyDescent="0.3">
@@ -23775,7 +23771,7 @@
         <v>1421</v>
       </c>
       <c r="G808" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="809" spans="1:7" x14ac:dyDescent="0.3">
@@ -23798,7 +23794,7 @@
         <v>1421</v>
       </c>
       <c r="G809" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="810" spans="1:7" x14ac:dyDescent="0.3">
@@ -23821,7 +23817,7 @@
         <v>1421</v>
       </c>
       <c r="G810" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="811" spans="1:7" x14ac:dyDescent="0.3">
@@ -23844,7 +23840,7 @@
         <v>1421</v>
       </c>
       <c r="G811" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="812" spans="1:7" x14ac:dyDescent="0.3">
@@ -23867,7 +23863,7 @@
         <v>1421</v>
       </c>
       <c r="G812" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="813" spans="1:7" x14ac:dyDescent="0.3">
@@ -23890,7 +23886,7 @@
         <v>1421</v>
       </c>
       <c r="G813" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="814" spans="1:7" x14ac:dyDescent="0.3">
@@ -23913,7 +23909,7 @@
         <v>1421</v>
       </c>
       <c r="G814" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="815" spans="1:7" x14ac:dyDescent="0.3">
@@ -23936,7 +23932,7 @@
         <v>1421</v>
       </c>
       <c r="G815" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="816" spans="1:7" x14ac:dyDescent="0.3">
@@ -23959,7 +23955,7 @@
         <v>1421</v>
       </c>
       <c r="G816" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="817" spans="1:7" x14ac:dyDescent="0.3">
@@ -23982,7 +23978,7 @@
         <v>1421</v>
       </c>
       <c r="G817" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="818" spans="1:7" x14ac:dyDescent="0.3">
@@ -24005,7 +24001,7 @@
         <v>1421</v>
       </c>
       <c r="G818" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="819" spans="1:7" x14ac:dyDescent="0.3">
@@ -24028,7 +24024,7 @@
         <v>1421</v>
       </c>
       <c r="G819" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="820" spans="1:7" x14ac:dyDescent="0.3">
@@ -24051,7 +24047,7 @@
         <v>1421</v>
       </c>
       <c r="G820" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="821" spans="1:7" x14ac:dyDescent="0.3">
@@ -24074,7 +24070,7 @@
         <v>1421</v>
       </c>
       <c r="G821" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="822" spans="1:7" x14ac:dyDescent="0.3">
@@ -24097,7 +24093,7 @@
         <v>1421</v>
       </c>
       <c r="G822" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="823" spans="1:7" x14ac:dyDescent="0.3">
@@ -24120,7 +24116,7 @@
         <v>1421</v>
       </c>
       <c r="G823" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="824" spans="1:7" x14ac:dyDescent="0.3">
@@ -24143,7 +24139,7 @@
         <v>1421</v>
       </c>
       <c r="G824" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="825" spans="1:7" x14ac:dyDescent="0.3">
@@ -24166,7 +24162,7 @@
         <v>1421</v>
       </c>
       <c r="G825" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="826" spans="1:7" x14ac:dyDescent="0.3">
@@ -24189,7 +24185,7 @@
         <v>1421</v>
       </c>
       <c r="G826" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="827" spans="1:7" x14ac:dyDescent="0.3">
@@ -24212,7 +24208,7 @@
         <v>1421</v>
       </c>
       <c r="G827" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="828" spans="1:7" x14ac:dyDescent="0.3">
@@ -24235,7 +24231,7 @@
         <v>1421</v>
       </c>
       <c r="G828" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="829" spans="1:7" x14ac:dyDescent="0.3">
@@ -24258,7 +24254,7 @@
         <v>1421</v>
       </c>
       <c r="G829" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="830" spans="1:7" x14ac:dyDescent="0.3">
@@ -24281,7 +24277,7 @@
         <v>1421</v>
       </c>
       <c r="G830" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="831" spans="1:7" x14ac:dyDescent="0.3">
@@ -24304,7 +24300,7 @@
         <v>1421</v>
       </c>
       <c r="G831" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="832" spans="1:7" x14ac:dyDescent="0.3">
@@ -24327,7 +24323,7 @@
         <v>1421</v>
       </c>
       <c r="G832" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="833" spans="1:7" x14ac:dyDescent="0.3">
@@ -24350,7 +24346,7 @@
         <v>1421</v>
       </c>
       <c r="G833" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="834" spans="1:7" x14ac:dyDescent="0.3">
@@ -24372,9 +24368,7 @@
       <c r="F834" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="G834" s="14" t="s">
-        <v>1462</v>
-      </c>
+      <c r="G834" s="14"/>
     </row>
     <row r="835" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A835" s="2">
@@ -24396,7 +24390,7 @@
         <v>1421</v>
       </c>
       <c r="G835" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="836" spans="1:7" x14ac:dyDescent="0.3">
@@ -24419,7 +24413,7 @@
         <v>1421</v>
       </c>
       <c r="G836" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="837" spans="1:7" x14ac:dyDescent="0.3">
@@ -24442,7 +24436,7 @@
         <v>1421</v>
       </c>
       <c r="G837" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="838" spans="1:7" x14ac:dyDescent="0.3">
@@ -24465,7 +24459,7 @@
         <v>1421</v>
       </c>
       <c r="G838" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="839" spans="1:7" x14ac:dyDescent="0.3">
@@ -24488,7 +24482,7 @@
         <v>1421</v>
       </c>
       <c r="G839" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="840" spans="1:7" x14ac:dyDescent="0.3">
@@ -24511,7 +24505,7 @@
         <v>1421</v>
       </c>
       <c r="G840" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="841" spans="1:7" x14ac:dyDescent="0.3">
@@ -24534,7 +24528,7 @@
         <v>1421</v>
       </c>
       <c r="G841" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="842" spans="1:7" x14ac:dyDescent="0.3">
@@ -24557,7 +24551,7 @@
         <v>1421</v>
       </c>
       <c r="G842" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="843" spans="1:7" x14ac:dyDescent="0.3">
@@ -24580,7 +24574,7 @@
         <v>1421</v>
       </c>
       <c r="G843" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="844" spans="1:7" x14ac:dyDescent="0.3">
@@ -24603,7 +24597,7 @@
         <v>1421</v>
       </c>
       <c r="G844" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="845" spans="1:7" x14ac:dyDescent="0.3">
@@ -24626,7 +24620,7 @@
         <v>1421</v>
       </c>
       <c r="G845" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="846" spans="1:7" x14ac:dyDescent="0.3">
@@ -24649,7 +24643,7 @@
         <v>1421</v>
       </c>
       <c r="G846" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="847" spans="1:7" x14ac:dyDescent="0.3">
@@ -24672,7 +24666,7 @@
         <v>1421</v>
       </c>
       <c r="G847" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="848" spans="1:7" x14ac:dyDescent="0.3">
@@ -24695,7 +24689,7 @@
         <v>1421</v>
       </c>
       <c r="G848" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="849" spans="1:7" x14ac:dyDescent="0.3">
@@ -24718,7 +24712,7 @@
         <v>1421</v>
       </c>
       <c r="G849" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="850" spans="1:7" x14ac:dyDescent="0.3">
@@ -24741,7 +24735,7 @@
         <v>1421</v>
       </c>
       <c r="G850" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="851" spans="1:7" x14ac:dyDescent="0.3">
@@ -24763,9 +24757,7 @@
       <c r="F851" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="G851" s="14" t="s">
-        <v>1462</v>
-      </c>
+      <c r="G851" s="14"/>
     </row>
     <row r="852" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A852" s="12">
@@ -24787,7 +24779,7 @@
         <v>1421</v>
       </c>
       <c r="G852" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="853" spans="1:7" x14ac:dyDescent="0.3">
@@ -24810,7 +24802,7 @@
         <v>1421</v>
       </c>
       <c r="G853" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="854" spans="1:7" x14ac:dyDescent="0.3">
@@ -24833,7 +24825,7 @@
         <v>1421</v>
       </c>
       <c r="G854" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="855" spans="1:7" x14ac:dyDescent="0.3">
@@ -28743,7 +28735,7 @@
         <v>1437</v>
       </c>
       <c r="G1024" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1025" spans="1:7" x14ac:dyDescent="0.3">
@@ -28766,7 +28758,7 @@
         <v>1437</v>
       </c>
       <c r="G1025" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.3">
@@ -28789,7 +28781,7 @@
         <v>1437</v>
       </c>
       <c r="G1026" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1027" spans="1:7" x14ac:dyDescent="0.3">
@@ -28812,7 +28804,7 @@
         <v>1437</v>
       </c>
       <c r="G1027" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1028" spans="1:7" x14ac:dyDescent="0.3">
@@ -28835,7 +28827,7 @@
         <v>1437</v>
       </c>
       <c r="G1028" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1029" spans="1:7" x14ac:dyDescent="0.3">
@@ -28858,7 +28850,7 @@
         <v>1437</v>
       </c>
       <c r="G1029" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1030" spans="1:7" x14ac:dyDescent="0.3">
@@ -28881,7 +28873,7 @@
         <v>1437</v>
       </c>
       <c r="G1030" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1031" spans="1:7" x14ac:dyDescent="0.3">
@@ -28904,7 +28896,7 @@
         <v>1437</v>
       </c>
       <c r="G1031" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1032" spans="1:7" x14ac:dyDescent="0.3">
@@ -28927,7 +28919,7 @@
         <v>1437</v>
       </c>
       <c r="G1032" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1033" spans="1:7" x14ac:dyDescent="0.3">
@@ -28950,7 +28942,7 @@
         <v>1437</v>
       </c>
       <c r="G1033" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1034" spans="1:7" x14ac:dyDescent="0.3">
@@ -28973,7 +28965,7 @@
         <v>1437</v>
       </c>
       <c r="G1034" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1035" spans="1:7" x14ac:dyDescent="0.3">
@@ -28996,7 +28988,7 @@
         <v>1437</v>
       </c>
       <c r="G1035" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1036" spans="1:7" x14ac:dyDescent="0.3">
@@ -29019,7 +29011,7 @@
         <v>1437</v>
       </c>
       <c r="G1036" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1037" spans="1:7" x14ac:dyDescent="0.3">
@@ -29042,7 +29034,7 @@
         <v>1437</v>
       </c>
       <c r="G1037" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1038" spans="1:7" x14ac:dyDescent="0.3">
@@ -29065,7 +29057,7 @@
         <v>1437</v>
       </c>
       <c r="G1038" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1039" spans="1:7" x14ac:dyDescent="0.3">
@@ -29088,7 +29080,7 @@
         <v>1437</v>
       </c>
       <c r="G1039" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1040" spans="1:7" x14ac:dyDescent="0.3">
@@ -29111,7 +29103,7 @@
         <v>1437</v>
       </c>
       <c r="G1040" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1041" spans="1:7" x14ac:dyDescent="0.3">
@@ -29134,7 +29126,7 @@
         <v>1437</v>
       </c>
       <c r="G1041" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1042" spans="1:7" x14ac:dyDescent="0.3">
@@ -29157,7 +29149,7 @@
         <v>1437</v>
       </c>
       <c r="G1042" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1043" spans="1:7" x14ac:dyDescent="0.3">
@@ -29180,7 +29172,7 @@
         <v>1437</v>
       </c>
       <c r="G1043" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1044" spans="1:7" x14ac:dyDescent="0.3">
@@ -29203,7 +29195,7 @@
         <v>1437</v>
       </c>
       <c r="G1044" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1045" spans="1:7" x14ac:dyDescent="0.3">
@@ -29226,7 +29218,7 @@
         <v>1437</v>
       </c>
       <c r="G1045" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1046" spans="1:7" x14ac:dyDescent="0.3">
@@ -29249,7 +29241,7 @@
         <v>1437</v>
       </c>
       <c r="G1046" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1047" spans="1:7" x14ac:dyDescent="0.3">
@@ -29272,7 +29264,7 @@
         <v>1437</v>
       </c>
       <c r="G1047" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1048" spans="1:7" x14ac:dyDescent="0.3">
@@ -29295,7 +29287,7 @@
         <v>1437</v>
       </c>
       <c r="G1048" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1049" spans="1:7" x14ac:dyDescent="0.3">
@@ -29318,7 +29310,7 @@
         <v>1437</v>
       </c>
       <c r="G1049" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1050" spans="1:7" x14ac:dyDescent="0.3">
@@ -29341,7 +29333,7 @@
         <v>1437</v>
       </c>
       <c r="G1050" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1051" spans="1:7" x14ac:dyDescent="0.3">
@@ -29364,7 +29356,7 @@
         <v>1437</v>
       </c>
       <c r="G1051" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1052" spans="1:7" x14ac:dyDescent="0.3">
@@ -29387,7 +29379,7 @@
         <v>1437</v>
       </c>
       <c r="G1052" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1053" spans="1:7" x14ac:dyDescent="0.3">
@@ -29410,7 +29402,7 @@
         <v>1437</v>
       </c>
       <c r="G1053" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1054" spans="1:7" x14ac:dyDescent="0.3">
@@ -29433,7 +29425,7 @@
         <v>1437</v>
       </c>
       <c r="G1054" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1055" spans="1:7" x14ac:dyDescent="0.3">
@@ -29456,7 +29448,7 @@
         <v>1437</v>
       </c>
       <c r="G1055" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1056" spans="1:7" x14ac:dyDescent="0.3">
@@ -29479,7 +29471,7 @@
         <v>1437</v>
       </c>
       <c r="G1056" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1057" spans="1:7" x14ac:dyDescent="0.3">
@@ -29502,7 +29494,7 @@
         <v>1437</v>
       </c>
       <c r="G1057" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
@@ -29525,7 +29517,7 @@
         <v>1437</v>
       </c>
       <c r="G1058" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
@@ -29548,7 +29540,7 @@
         <v>1437</v>
       </c>
       <c r="G1059" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1060" spans="1:7" x14ac:dyDescent="0.3">
@@ -29571,7 +29563,7 @@
         <v>1437</v>
       </c>
       <c r="G1060" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1061" spans="1:7" x14ac:dyDescent="0.3">
@@ -29594,7 +29586,7 @@
         <v>1437</v>
       </c>
       <c r="G1061" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
@@ -29617,7 +29609,7 @@
         <v>1437</v>
       </c>
       <c r="G1062" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
@@ -29640,7 +29632,7 @@
         <v>1437</v>
       </c>
       <c r="G1063" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1064" spans="1:7" x14ac:dyDescent="0.3">
@@ -29663,7 +29655,7 @@
         <v>1437</v>
       </c>
       <c r="G1064" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1065" spans="1:7" x14ac:dyDescent="0.3">
@@ -29686,7 +29678,7 @@
         <v>1437</v>
       </c>
       <c r="G1065" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1066" spans="1:7" x14ac:dyDescent="0.3">
@@ -29709,7 +29701,7 @@
         <v>1437</v>
       </c>
       <c r="G1066" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1067" spans="1:7" x14ac:dyDescent="0.3">
@@ -29732,7 +29724,7 @@
         <v>1437</v>
       </c>
       <c r="G1067" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1068" spans="1:7" x14ac:dyDescent="0.3">
@@ -29755,7 +29747,7 @@
         <v>1437</v>
       </c>
       <c r="G1068" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1069" spans="1:7" x14ac:dyDescent="0.3">
@@ -29778,7 +29770,7 @@
         <v>1437</v>
       </c>
       <c r="G1069" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.3">
@@ -29801,7 +29793,7 @@
         <v>1437</v>
       </c>
       <c r="G1070" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1071" spans="1:7" x14ac:dyDescent="0.3">
@@ -29824,7 +29816,7 @@
         <v>1437</v>
       </c>
       <c r="G1071" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1072" spans="1:7" x14ac:dyDescent="0.3">
@@ -29847,7 +29839,7 @@
         <v>1437</v>
       </c>
       <c r="G1072" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1073" spans="1:7" x14ac:dyDescent="0.3">
@@ -29870,7 +29862,7 @@
         <v>1437</v>
       </c>
       <c r="G1073" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.3">
@@ -29893,7 +29885,7 @@
         <v>1437</v>
       </c>
       <c r="G1074" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1075" spans="1:7" x14ac:dyDescent="0.3">
@@ -29916,7 +29908,7 @@
         <v>1437</v>
       </c>
       <c r="G1075" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1076" spans="1:7" x14ac:dyDescent="0.3">
@@ -29939,7 +29931,7 @@
         <v>1437</v>
       </c>
       <c r="G1076" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1077" spans="1:7" x14ac:dyDescent="0.3">
@@ -29962,7 +29954,7 @@
         <v>1437</v>
       </c>
       <c r="G1077" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.3">
@@ -29985,7 +29977,7 @@
         <v>1437</v>
       </c>
       <c r="G1078" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.3">
@@ -30008,7 +30000,7 @@
         <v>1437</v>
       </c>
       <c r="G1079" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1080" spans="1:7" x14ac:dyDescent="0.3">
@@ -30031,7 +30023,7 @@
         <v>1437</v>
       </c>
       <c r="G1080" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1081" spans="1:7" x14ac:dyDescent="0.3">
@@ -30054,7 +30046,7 @@
         <v>1437</v>
       </c>
       <c r="G1081" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1082" spans="1:7" x14ac:dyDescent="0.3">
@@ -30077,7 +30069,7 @@
         <v>1437</v>
       </c>
       <c r="G1082" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1083" spans="1:7" x14ac:dyDescent="0.3">
@@ -30100,7 +30092,7 @@
         <v>1437</v>
       </c>
       <c r="G1083" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1084" spans="1:7" x14ac:dyDescent="0.3">
@@ -30123,7 +30115,7 @@
         <v>1437</v>
       </c>
       <c r="G1084" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1085" spans="1:7" x14ac:dyDescent="0.3">
@@ -30146,7 +30138,7 @@
         <v>1437</v>
       </c>
       <c r="G1085" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1086" spans="1:7" x14ac:dyDescent="0.3">
@@ -30169,7 +30161,7 @@
         <v>1437</v>
       </c>
       <c r="G1086" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.3">
@@ -30192,7 +30184,7 @@
         <v>1437</v>
       </c>
       <c r="G1087" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1088" spans="1:7" x14ac:dyDescent="0.3">
@@ -30215,7 +30207,7 @@
         <v>1437</v>
       </c>
       <c r="G1088" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1089" spans="1:7" x14ac:dyDescent="0.3">
@@ -30238,7 +30230,7 @@
         <v>1437</v>
       </c>
       <c r="G1089" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1090" spans="1:7" x14ac:dyDescent="0.3">
@@ -30261,7 +30253,7 @@
         <v>1437</v>
       </c>
       <c r="G1090" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1091" spans="1:7" x14ac:dyDescent="0.3">
@@ -30284,7 +30276,7 @@
         <v>1437</v>
       </c>
       <c r="G1091" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1092" spans="1:7" x14ac:dyDescent="0.3">
@@ -30307,7 +30299,7 @@
         <v>1437</v>
       </c>
       <c r="G1092" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
@@ -30330,7 +30322,7 @@
         <v>1437</v>
       </c>
       <c r="G1093" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1094" spans="1:7" x14ac:dyDescent="0.3">
@@ -30353,7 +30345,7 @@
         <v>1437</v>
       </c>
       <c r="G1094" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1095" spans="1:7" x14ac:dyDescent="0.3">
@@ -30376,7 +30368,7 @@
         <v>1437</v>
       </c>
       <c r="G1095" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1096" spans="1:7" x14ac:dyDescent="0.3">
@@ -30399,7 +30391,7 @@
         <v>1437</v>
       </c>
       <c r="G1096" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1097" spans="1:7" x14ac:dyDescent="0.3">
@@ -30422,7 +30414,7 @@
         <v>1437</v>
       </c>
       <c r="G1097" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1098" spans="1:7" x14ac:dyDescent="0.3">
@@ -30445,7 +30437,7 @@
         <v>1437</v>
       </c>
       <c r="G1098" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1099" spans="1:7" x14ac:dyDescent="0.3">
@@ -30468,7 +30460,7 @@
         <v>1437</v>
       </c>
       <c r="G1099" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1100" spans="1:7" x14ac:dyDescent="0.3">
@@ -30491,7 +30483,7 @@
         <v>1437</v>
       </c>
       <c r="G1100" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1101" spans="1:7" x14ac:dyDescent="0.3">
@@ -30514,7 +30506,7 @@
         <v>1437</v>
       </c>
       <c r="G1101" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1102" spans="1:7" x14ac:dyDescent="0.3">
@@ -30537,7 +30529,7 @@
         <v>1437</v>
       </c>
       <c r="G1102" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1103" spans="1:7" x14ac:dyDescent="0.3">
@@ -30560,7 +30552,7 @@
         <v>1437</v>
       </c>
       <c r="G1103" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.3">
@@ -30583,7 +30575,7 @@
         <v>1437</v>
       </c>
       <c r="G1104" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1105" spans="1:7" x14ac:dyDescent="0.3">
@@ -30606,7 +30598,7 @@
         <v>1437</v>
       </c>
       <c r="G1105" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1106" spans="1:7" x14ac:dyDescent="0.3">
@@ -30629,7 +30621,7 @@
         <v>1437</v>
       </c>
       <c r="G1106" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1107" spans="1:7" x14ac:dyDescent="0.3">
@@ -30652,7 +30644,7 @@
         <v>1437</v>
       </c>
       <c r="G1107" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1108" spans="1:7" x14ac:dyDescent="0.3">
@@ -30675,7 +30667,7 @@
         <v>1437</v>
       </c>
       <c r="G1108" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1109" spans="1:7" x14ac:dyDescent="0.3">
@@ -30698,7 +30690,7 @@
         <v>1437</v>
       </c>
       <c r="G1109" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1110" spans="1:7" x14ac:dyDescent="0.3">
@@ -30721,7 +30713,7 @@
         <v>1437</v>
       </c>
       <c r="G1110" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1111" spans="1:7" x14ac:dyDescent="0.3">
@@ -30744,7 +30736,7 @@
         <v>1437</v>
       </c>
       <c r="G1111" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1112" spans="1:7" x14ac:dyDescent="0.3">
@@ -30767,7 +30759,7 @@
         <v>1437</v>
       </c>
       <c r="G1112" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1113" spans="1:7" x14ac:dyDescent="0.3">
@@ -30790,7 +30782,7 @@
         <v>1437</v>
       </c>
       <c r="G1113" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.3">
@@ -30813,7 +30805,7 @@
         <v>1437</v>
       </c>
       <c r="G1114" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.3">
@@ -30836,7 +30828,7 @@
         <v>1437</v>
       </c>
       <c r="G1115" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1116" spans="1:7" x14ac:dyDescent="0.3">
@@ -30859,7 +30851,7 @@
         <v>1437</v>
       </c>
       <c r="G1116" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1117" spans="1:7" x14ac:dyDescent="0.3">
@@ -30882,7 +30874,7 @@
         <v>1437</v>
       </c>
       <c r="G1117" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1118" spans="1:7" x14ac:dyDescent="0.3">
@@ -30905,7 +30897,7 @@
         <v>1437</v>
       </c>
       <c r="G1118" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1119" spans="1:7" x14ac:dyDescent="0.3">
@@ -30928,7 +30920,7 @@
         <v>1437</v>
       </c>
       <c r="G1119" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1120" spans="1:7" x14ac:dyDescent="0.3">
@@ -30951,7 +30943,7 @@
         <v>1437</v>
       </c>
       <c r="G1120" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1121" spans="1:7" x14ac:dyDescent="0.3">
@@ -30974,7 +30966,7 @@
         <v>1437</v>
       </c>
       <c r="G1121" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1122" spans="1:7" x14ac:dyDescent="0.3">
@@ -30997,7 +30989,7 @@
         <v>1437</v>
       </c>
       <c r="G1122" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1123" spans="1:7" x14ac:dyDescent="0.3">
@@ -31020,7 +31012,7 @@
         <v>1437</v>
       </c>
       <c r="G1123" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1124" spans="1:7" x14ac:dyDescent="0.3">
@@ -31043,7 +31035,7 @@
         <v>1437</v>
       </c>
       <c r="G1124" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1125" spans="1:7" x14ac:dyDescent="0.3">
@@ -31066,7 +31058,7 @@
         <v>1437</v>
       </c>
       <c r="G1125" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1126" spans="1:7" x14ac:dyDescent="0.3">
@@ -31089,7 +31081,7 @@
         <v>1437</v>
       </c>
       <c r="G1126" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1127" spans="1:7" x14ac:dyDescent="0.3">
@@ -31112,7 +31104,7 @@
         <v>1437</v>
       </c>
       <c r="G1127" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1128" spans="1:7" x14ac:dyDescent="0.3">
@@ -31135,7 +31127,7 @@
         <v>1437</v>
       </c>
       <c r="G1128" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1129" spans="1:7" x14ac:dyDescent="0.3">
@@ -31158,7 +31150,7 @@
         <v>1437</v>
       </c>
       <c r="G1129" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.3">
@@ -31181,7 +31173,7 @@
         <v>1437</v>
       </c>
       <c r="G1130" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1131" spans="1:7" x14ac:dyDescent="0.3">
@@ -31204,7 +31196,7 @@
         <v>1437</v>
       </c>
       <c r="G1131" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1132" spans="1:7" x14ac:dyDescent="0.3">
@@ -31227,7 +31219,7 @@
         <v>1437</v>
       </c>
       <c r="G1132" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1133" spans="1:7" x14ac:dyDescent="0.3">
@@ -31250,7 +31242,7 @@
         <v>1437</v>
       </c>
       <c r="G1133" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1134" spans="1:7" x14ac:dyDescent="0.3">
@@ -31273,7 +31265,7 @@
         <v>1437</v>
       </c>
       <c r="G1134" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1135" spans="1:7" x14ac:dyDescent="0.3">
@@ -31296,7 +31288,7 @@
         <v>1437</v>
       </c>
       <c r="G1135" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1136" spans="1:7" x14ac:dyDescent="0.3">
@@ -31319,7 +31311,7 @@
         <v>1437</v>
       </c>
       <c r="G1136" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1137" spans="1:7" x14ac:dyDescent="0.3">
@@ -31342,7 +31334,7 @@
         <v>1437</v>
       </c>
       <c r="G1137" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1138" spans="1:7" x14ac:dyDescent="0.3">
@@ -31365,7 +31357,7 @@
         <v>1437</v>
       </c>
       <c r="G1138" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1139" spans="1:7" x14ac:dyDescent="0.3">
@@ -31388,7 +31380,7 @@
         <v>1437</v>
       </c>
       <c r="G1139" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1140" spans="1:7" x14ac:dyDescent="0.3">
@@ -31411,7 +31403,7 @@
         <v>1437</v>
       </c>
       <c r="G1140" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1141" spans="1:7" x14ac:dyDescent="0.3">
@@ -31434,7 +31426,7 @@
         <v>1437</v>
       </c>
       <c r="G1141" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1142" spans="1:7" x14ac:dyDescent="0.3">
@@ -31457,7 +31449,7 @@
         <v>1437</v>
       </c>
       <c r="G1142" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1143" spans="1:7" x14ac:dyDescent="0.3">
@@ -31480,7 +31472,7 @@
         <v>1437</v>
       </c>
       <c r="G1143" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.3">
@@ -31503,7 +31495,7 @@
         <v>1437</v>
       </c>
       <c r="G1144" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1145" spans="1:7" x14ac:dyDescent="0.3">
@@ -31526,7 +31518,7 @@
         <v>1437</v>
       </c>
       <c r="G1145" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1146" spans="1:7" x14ac:dyDescent="0.3">
@@ -31549,7 +31541,7 @@
         <v>1437</v>
       </c>
       <c r="G1146" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1147" spans="1:7" x14ac:dyDescent="0.3">
@@ -31572,7 +31564,7 @@
         <v>1437</v>
       </c>
       <c r="G1147" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1148" spans="1:7" x14ac:dyDescent="0.3">
@@ -31595,7 +31587,7 @@
         <v>1437</v>
       </c>
       <c r="G1148" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1149" spans="1:7" x14ac:dyDescent="0.3">
@@ -31618,7 +31610,7 @@
         <v>1437</v>
       </c>
       <c r="G1149" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1150" spans="1:7" x14ac:dyDescent="0.3">
@@ -31641,7 +31633,7 @@
         <v>1437</v>
       </c>
       <c r="G1150" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1151" spans="1:7" x14ac:dyDescent="0.3">
@@ -31664,7 +31656,7 @@
         <v>1437</v>
       </c>
       <c r="G1151" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.3">
@@ -31687,7 +31679,7 @@
         <v>1437</v>
       </c>
       <c r="G1152" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1153" spans="1:7" x14ac:dyDescent="0.3">
@@ -31710,7 +31702,7 @@
         <v>1437</v>
       </c>
       <c r="G1153" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1154" spans="1:7" x14ac:dyDescent="0.3">
@@ -31733,7 +31725,7 @@
         <v>1437</v>
       </c>
       <c r="G1154" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1155" spans="1:7" x14ac:dyDescent="0.3">
@@ -31756,7 +31748,7 @@
         <v>1437</v>
       </c>
       <c r="G1155" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1156" spans="1:7" x14ac:dyDescent="0.3">
@@ -31779,7 +31771,7 @@
         <v>1437</v>
       </c>
       <c r="G1156" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1157" spans="1:7" x14ac:dyDescent="0.3">
@@ -31802,7 +31794,7 @@
         <v>1437</v>
       </c>
       <c r="G1157" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1158" spans="1:7" x14ac:dyDescent="0.3">
@@ -31825,7 +31817,7 @@
         <v>1437</v>
       </c>
       <c r="G1158" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1159" spans="1:7" x14ac:dyDescent="0.3">
@@ -31848,7 +31840,7 @@
         <v>1437</v>
       </c>
       <c r="G1159" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1160" spans="1:7" x14ac:dyDescent="0.3">
@@ -31871,7 +31863,7 @@
         <v>1437</v>
       </c>
       <c r="G1160" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1161" spans="1:7" x14ac:dyDescent="0.3">
@@ -31894,7 +31886,7 @@
         <v>1437</v>
       </c>
       <c r="G1161" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1162" spans="1:7" x14ac:dyDescent="0.3">
@@ -31917,7 +31909,7 @@
         <v>1437</v>
       </c>
       <c r="G1162" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1163" spans="1:7" x14ac:dyDescent="0.3">
@@ -31940,7 +31932,7 @@
         <v>1437</v>
       </c>
       <c r="G1163" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1164" spans="1:7" x14ac:dyDescent="0.3">
@@ -31963,7 +31955,7 @@
         <v>1437</v>
       </c>
       <c r="G1164" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1165" spans="1:7" x14ac:dyDescent="0.3">
@@ -31986,7 +31978,7 @@
         <v>1437</v>
       </c>
       <c r="G1165" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.3">
@@ -32009,7 +32001,7 @@
         <v>1437</v>
       </c>
       <c r="G1166" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1167" spans="1:7" x14ac:dyDescent="0.3">
@@ -32032,7 +32024,7 @@
         <v>1437</v>
       </c>
       <c r="G1167" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1168" spans="1:7" x14ac:dyDescent="0.3">
@@ -32055,7 +32047,7 @@
         <v>1437</v>
       </c>
       <c r="G1168" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1169" spans="1:7" x14ac:dyDescent="0.3">
@@ -32078,7 +32070,7 @@
         <v>1437</v>
       </c>
       <c r="G1169" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1170" spans="1:7" x14ac:dyDescent="0.3">
@@ -32101,7 +32093,7 @@
         <v>1437</v>
       </c>
       <c r="G1170" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1171" spans="1:7" x14ac:dyDescent="0.3">
@@ -32124,7 +32116,7 @@
         <v>1437</v>
       </c>
       <c r="G1171" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1172" spans="1:7" x14ac:dyDescent="0.3">
@@ -32147,7 +32139,7 @@
         <v>1437</v>
       </c>
       <c r="G1172" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1173" spans="1:7" x14ac:dyDescent="0.3">
@@ -32170,7 +32162,7 @@
         <v>1437</v>
       </c>
       <c r="G1173" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1174" spans="1:7" x14ac:dyDescent="0.3">
@@ -32193,7 +32185,7 @@
         <v>1437</v>
       </c>
       <c r="G1174" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1175" spans="1:7" x14ac:dyDescent="0.3">
@@ -32216,7 +32208,7 @@
         <v>1437</v>
       </c>
       <c r="G1175" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1176" spans="1:7" x14ac:dyDescent="0.3">
@@ -32239,7 +32231,7 @@
         <v>1437</v>
       </c>
       <c r="G1176" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1177" spans="1:7" x14ac:dyDescent="0.3">
@@ -32262,7 +32254,7 @@
         <v>1437</v>
       </c>
       <c r="G1177" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1178" spans="1:7" x14ac:dyDescent="0.3">
@@ -32285,7 +32277,7 @@
         <v>1437</v>
       </c>
       <c r="G1178" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1179" spans="1:7" x14ac:dyDescent="0.3">
@@ -32308,7 +32300,7 @@
         <v>1437</v>
       </c>
       <c r="G1179" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1180" spans="1:7" x14ac:dyDescent="0.3">
@@ -32331,7 +32323,7 @@
         <v>1437</v>
       </c>
       <c r="G1180" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1181" spans="1:7" x14ac:dyDescent="0.3">
@@ -32354,7 +32346,7 @@
         <v>1437</v>
       </c>
       <c r="G1181" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1182" spans="1:7" x14ac:dyDescent="0.3">
@@ -32377,7 +32369,7 @@
         <v>1437</v>
       </c>
       <c r="G1182" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1183" spans="1:7" x14ac:dyDescent="0.3">
@@ -32400,7 +32392,7 @@
         <v>1437</v>
       </c>
       <c r="G1183" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1184" spans="1:7" x14ac:dyDescent="0.3">
@@ -32423,7 +32415,7 @@
         <v>1437</v>
       </c>
       <c r="G1184" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1185" spans="1:7" x14ac:dyDescent="0.3">
@@ -32446,7 +32438,7 @@
         <v>1437</v>
       </c>
       <c r="G1185" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1186" spans="1:7" x14ac:dyDescent="0.3">
@@ -32469,7 +32461,7 @@
         <v>1437</v>
       </c>
       <c r="G1186" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1187" spans="1:7" x14ac:dyDescent="0.3">
@@ -32492,7 +32484,7 @@
         <v>1437</v>
       </c>
       <c r="G1187" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1188" spans="1:7" x14ac:dyDescent="0.3">
@@ -32515,7 +32507,7 @@
         <v>1437</v>
       </c>
       <c r="G1188" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1189" spans="1:7" x14ac:dyDescent="0.3">
@@ -32538,7 +32530,7 @@
         <v>1437</v>
       </c>
       <c r="G1189" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1190" spans="1:7" x14ac:dyDescent="0.3">
@@ -32561,7 +32553,7 @@
         <v>1437</v>
       </c>
       <c r="G1190" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1191" spans="1:7" x14ac:dyDescent="0.3">
@@ -32584,7 +32576,7 @@
         <v>1437</v>
       </c>
       <c r="G1191" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1192" spans="1:7" x14ac:dyDescent="0.3">
@@ -32607,7 +32599,7 @@
         <v>1437</v>
       </c>
       <c r="G1192" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1193" spans="1:7" x14ac:dyDescent="0.3">
@@ -32630,7 +32622,7 @@
         <v>1437</v>
       </c>
       <c r="G1193" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1194" spans="1:7" x14ac:dyDescent="0.3">
@@ -32653,7 +32645,7 @@
         <v>1437</v>
       </c>
       <c r="G1194" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1195" spans="1:7" x14ac:dyDescent="0.3">
@@ -32676,7 +32668,7 @@
         <v>1437</v>
       </c>
       <c r="G1195" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.3">
@@ -32699,7 +32691,7 @@
         <v>1437</v>
       </c>
       <c r="G1196" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1197" spans="1:7" x14ac:dyDescent="0.3">
@@ -32722,7 +32714,7 @@
         <v>1437</v>
       </c>
       <c r="G1197" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1198" spans="1:7" x14ac:dyDescent="0.3">
@@ -32745,7 +32737,7 @@
         <v>1437</v>
       </c>
       <c r="G1198" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1199" spans="1:7" x14ac:dyDescent="0.3">
@@ -32768,7 +32760,7 @@
         <v>1437</v>
       </c>
       <c r="G1199" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1200" spans="1:7" x14ac:dyDescent="0.3">
@@ -32791,7 +32783,7 @@
         <v>1437</v>
       </c>
       <c r="G1200" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1201" spans="1:7" x14ac:dyDescent="0.3">
@@ -32814,7 +32806,7 @@
         <v>1437</v>
       </c>
       <c r="G1201" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1202" spans="1:7" x14ac:dyDescent="0.3">
@@ -32837,7 +32829,7 @@
         <v>1437</v>
       </c>
       <c r="G1202" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1203" spans="1:7" x14ac:dyDescent="0.3">
@@ -32860,7 +32852,7 @@
         <v>1437</v>
       </c>
       <c r="G1203" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1204" spans="1:7" x14ac:dyDescent="0.3">
@@ -32883,7 +32875,7 @@
         <v>1437</v>
       </c>
       <c r="G1204" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1205" spans="1:7" x14ac:dyDescent="0.3">
@@ -32906,7 +32898,7 @@
         <v>1437</v>
       </c>
       <c r="G1205" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1206" spans="1:7" x14ac:dyDescent="0.3">
@@ -32929,7 +32921,7 @@
         <v>1437</v>
       </c>
       <c r="G1206" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.3">
@@ -32952,7 +32944,7 @@
         <v>1437</v>
       </c>
       <c r="G1207" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1208" spans="1:7" x14ac:dyDescent="0.3">
@@ -32975,7 +32967,7 @@
         <v>1437</v>
       </c>
       <c r="G1208" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1209" spans="1:7" x14ac:dyDescent="0.3">
@@ -32998,7 +32990,7 @@
         <v>1437</v>
       </c>
       <c r="G1209" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1210" spans="1:7" x14ac:dyDescent="0.3">
@@ -33021,7 +33013,7 @@
         <v>1437</v>
       </c>
       <c r="G1210" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1211" spans="1:7" x14ac:dyDescent="0.3">
@@ -33044,7 +33036,7 @@
         <v>1437</v>
       </c>
       <c r="G1211" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1212" spans="1:7" x14ac:dyDescent="0.3">
@@ -33067,7 +33059,7 @@
         <v>1437</v>
       </c>
       <c r="G1212" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1213" spans="1:7" x14ac:dyDescent="0.3">
@@ -33090,7 +33082,7 @@
         <v>1437</v>
       </c>
       <c r="G1213" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1214" spans="1:7" x14ac:dyDescent="0.3">
@@ -33113,7 +33105,7 @@
         <v>1437</v>
       </c>
       <c r="G1214" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1215" spans="1:7" x14ac:dyDescent="0.3">
@@ -33136,7 +33128,7 @@
         <v>1437</v>
       </c>
       <c r="G1215" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1216" spans="1:7" x14ac:dyDescent="0.3">
@@ -33159,7 +33151,7 @@
         <v>1437</v>
       </c>
       <c r="G1216" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
@@ -33182,7 +33174,7 @@
         <v>1437</v>
       </c>
       <c r="G1217" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1218" spans="1:7" x14ac:dyDescent="0.3">
@@ -33205,7 +33197,7 @@
         <v>1437</v>
       </c>
       <c r="G1218" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1219" spans="1:7" x14ac:dyDescent="0.3">
@@ -33228,7 +33220,7 @@
         <v>1437</v>
       </c>
       <c r="G1219" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1220" spans="1:7" x14ac:dyDescent="0.3">
@@ -33251,7 +33243,7 @@
         <v>1437</v>
       </c>
       <c r="G1220" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1221" spans="1:7" x14ac:dyDescent="0.3">
@@ -33274,7 +33266,7 @@
         <v>1437</v>
       </c>
       <c r="G1221" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1222" spans="1:7" x14ac:dyDescent="0.3">
@@ -33297,7 +33289,7 @@
         <v>1437</v>
       </c>
       <c r="G1222" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1223" spans="1:7" x14ac:dyDescent="0.3">
@@ -33320,7 +33312,7 @@
         <v>1437</v>
       </c>
       <c r="G1223" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1224" spans="1:7" x14ac:dyDescent="0.3">
@@ -33343,7 +33335,7 @@
         <v>1437</v>
       </c>
       <c r="G1224" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1225" spans="1:7" x14ac:dyDescent="0.3">
@@ -33366,7 +33358,7 @@
         <v>1437</v>
       </c>
       <c r="G1225" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1226" spans="1:7" x14ac:dyDescent="0.3">
@@ -33389,7 +33381,7 @@
         <v>1437</v>
       </c>
       <c r="G1226" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1227" spans="1:7" x14ac:dyDescent="0.3">
@@ -33412,7 +33404,7 @@
         <v>1437</v>
       </c>
       <c r="G1227" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1228" spans="1:7" x14ac:dyDescent="0.3">
@@ -33435,7 +33427,7 @@
         <v>1437</v>
       </c>
       <c r="G1228" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
@@ -33458,7 +33450,7 @@
         <v>1437</v>
       </c>
       <c r="G1229" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1230" spans="1:7" x14ac:dyDescent="0.3">
@@ -33481,7 +33473,7 @@
         <v>1437</v>
       </c>
       <c r="G1230" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1231" spans="1:7" x14ac:dyDescent="0.3">
@@ -33504,7 +33496,7 @@
         <v>1437</v>
       </c>
       <c r="G1231" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1232" spans="1:7" x14ac:dyDescent="0.3">
@@ -33527,7 +33519,7 @@
         <v>1437</v>
       </c>
       <c r="G1232" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1233" spans="1:7" x14ac:dyDescent="0.3">
@@ -33550,7 +33542,7 @@
         <v>1437</v>
       </c>
       <c r="G1233" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1234" spans="1:7" x14ac:dyDescent="0.3">
@@ -33573,7 +33565,7 @@
         <v>1437</v>
       </c>
       <c r="G1234" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1235" spans="1:7" x14ac:dyDescent="0.3">
@@ -33596,7 +33588,7 @@
         <v>1437</v>
       </c>
       <c r="G1235" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1236" spans="1:7" x14ac:dyDescent="0.3">
@@ -33619,7 +33611,7 @@
         <v>1437</v>
       </c>
       <c r="G1236" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1237" spans="1:7" x14ac:dyDescent="0.3">
@@ -33642,7 +33634,7 @@
         <v>1437</v>
       </c>
       <c r="G1237" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1238" spans="1:7" x14ac:dyDescent="0.3">
@@ -33665,7 +33657,7 @@
         <v>1437</v>
       </c>
       <c r="G1238" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1239" spans="1:7" x14ac:dyDescent="0.3">
@@ -33688,7 +33680,7 @@
         <v>1437</v>
       </c>
       <c r="G1239" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1240" spans="1:7" x14ac:dyDescent="0.3">
@@ -33711,7 +33703,7 @@
         <v>1437</v>
       </c>
       <c r="G1240" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1241" spans="1:7" x14ac:dyDescent="0.3">
@@ -33734,7 +33726,7 @@
         <v>1437</v>
       </c>
       <c r="G1241" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1242" spans="1:7" x14ac:dyDescent="0.3">
@@ -33757,7 +33749,7 @@
         <v>1437</v>
       </c>
       <c r="G1242" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1243" spans="1:7" x14ac:dyDescent="0.3">
@@ -33780,7 +33772,7 @@
         <v>1437</v>
       </c>
       <c r="G1243" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1244" spans="1:7" x14ac:dyDescent="0.3">
@@ -33803,7 +33795,7 @@
         <v>1437</v>
       </c>
       <c r="G1244" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1245" spans="1:7" x14ac:dyDescent="0.3">
@@ -33826,7 +33818,7 @@
         <v>1437</v>
       </c>
       <c r="G1245" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1246" spans="1:7" x14ac:dyDescent="0.3">
@@ -33849,7 +33841,7 @@
         <v>1437</v>
       </c>
       <c r="G1246" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1247" spans="1:7" x14ac:dyDescent="0.3">
@@ -33872,7 +33864,7 @@
         <v>1437</v>
       </c>
       <c r="G1247" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1248" spans="1:7" x14ac:dyDescent="0.3">
@@ -33895,7 +33887,7 @@
         <v>1437</v>
       </c>
       <c r="G1248" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1249" spans="1:7" x14ac:dyDescent="0.3">
@@ -33918,7 +33910,7 @@
         <v>1437</v>
       </c>
       <c r="G1249" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1250" spans="1:7" x14ac:dyDescent="0.3">
@@ -33941,7 +33933,7 @@
         <v>1437</v>
       </c>
       <c r="G1250" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1251" spans="1:7" x14ac:dyDescent="0.3">
@@ -33964,7 +33956,7 @@
         <v>1437</v>
       </c>
       <c r="G1251" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1252" spans="1:7" x14ac:dyDescent="0.3">
@@ -33987,7 +33979,7 @@
         <v>1437</v>
       </c>
       <c r="G1252" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1253" spans="1:7" x14ac:dyDescent="0.3">
@@ -34010,7 +34002,7 @@
         <v>1437</v>
       </c>
       <c r="G1253" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1254" spans="1:7" x14ac:dyDescent="0.3">
@@ -34033,7 +34025,7 @@
         <v>1437</v>
       </c>
       <c r="G1254" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1255" spans="1:7" x14ac:dyDescent="0.3">
@@ -34056,7 +34048,7 @@
         <v>1437</v>
       </c>
       <c r="G1255" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1256" spans="1:7" x14ac:dyDescent="0.3">
@@ -34079,7 +34071,7 @@
         <v>1437</v>
       </c>
       <c r="G1256" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1257" spans="1:7" x14ac:dyDescent="0.3">
@@ -34102,7 +34094,7 @@
         <v>1437</v>
       </c>
       <c r="G1257" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1258" spans="1:7" x14ac:dyDescent="0.3">
@@ -34125,7 +34117,7 @@
         <v>1437</v>
       </c>
       <c r="G1258" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1259" spans="1:7" x14ac:dyDescent="0.3">
@@ -34148,7 +34140,7 @@
         <v>1437</v>
       </c>
       <c r="G1259" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1260" spans="1:7" x14ac:dyDescent="0.3">
@@ -34171,7 +34163,7 @@
         <v>1437</v>
       </c>
       <c r="G1260" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1261" spans="1:7" x14ac:dyDescent="0.3">
@@ -34194,7 +34186,7 @@
         <v>1437</v>
       </c>
       <c r="G1261" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1262" spans="1:7" x14ac:dyDescent="0.3">
@@ -34217,7 +34209,7 @@
         <v>1437</v>
       </c>
       <c r="G1262" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1263" spans="1:7" x14ac:dyDescent="0.3">
@@ -34240,7 +34232,7 @@
         <v>1437</v>
       </c>
       <c r="G1263" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1264" spans="1:7" x14ac:dyDescent="0.3">
@@ -34263,7 +34255,7 @@
         <v>1437</v>
       </c>
       <c r="G1264" s="14" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1265" spans="1:7" x14ac:dyDescent="0.3">
